--- a/input_data/admin_data/DOM/_clean/total-pre-DOM.xlsx
+++ b/input_data/admin_data/DOM/_clean/total-pre-DOM.xlsx
@@ -21,7 +21,1735 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21632" uniqueCount="15296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22208" uniqueCount="15872">
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>pretax</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>pretax</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>pretax</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>pretax</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>pretax</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>pretax</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>pretax</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>pretax</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>DOM</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>component</t>
+  </si>
+  <si>
+    <t>pretax</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>totalpop</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>thr</t>
+  </si>
+  <si>
+    <t>bracketavg</t>
+  </si>
   <si>
     <t>year</t>
   </si>
@@ -45957,28 +47685,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15232</v>
+        <v>15296</v>
       </c>
       <c r="B1" t="s">
-        <v>15233</v>
+        <v>15297</v>
       </c>
       <c r="C1" t="s">
-        <v>15262</v>
+        <v>15326</v>
       </c>
       <c r="D1" t="s">
-        <v>15291</v>
+        <v>15355</v>
       </c>
       <c r="E1" t="s">
-        <v>15292</v>
+        <v>15356</v>
       </c>
       <c r="F1" t="s">
-        <v>15293</v>
+        <v>15357</v>
       </c>
       <c r="G1" t="s">
-        <v>15294</v>
+        <v>15358</v>
       </c>
       <c r="H1" t="s">
-        <v>15295</v>
+        <v>15359</v>
       </c>
     </row>
     <row r="2">
@@ -45986,10 +47714,10 @@
         <v>2012</v>
       </c>
       <c r="B2" t="s">
-        <v>15234</v>
+        <v>15298</v>
       </c>
       <c r="C2" t="s">
-        <v>15263</v>
+        <v>15327</v>
       </c>
       <c r="D2">
         <v>10070411</v>
@@ -46010,10 +47738,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15290</v>
+        <v>15299</v>
       </c>
       <c r="C3" t="s">
-        <v>15290</v>
+        <v>15328</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -46030,10 +47758,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15290</v>
+        <v>15300</v>
       </c>
       <c r="C4" t="s">
-        <v>15290</v>
+        <v>15329</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -46050,10 +47778,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15290</v>
+        <v>15301</v>
       </c>
       <c r="C5" t="s">
-        <v>15290</v>
+        <v>15330</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -46070,10 +47798,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15290</v>
+        <v>15302</v>
       </c>
       <c r="C6" t="s">
-        <v>15290</v>
+        <v>15331</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -46090,10 +47818,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15290</v>
+        <v>15303</v>
       </c>
       <c r="C7" t="s">
-        <v>15290</v>
+        <v>15332</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -46110,10 +47838,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15290</v>
+        <v>15304</v>
       </c>
       <c r="C8" t="s">
-        <v>15290</v>
+        <v>15333</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -46130,10 +47858,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15290</v>
+        <v>15305</v>
       </c>
       <c r="C9" t="s">
-        <v>15290</v>
+        <v>15334</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -46150,10 +47878,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15290</v>
+        <v>15306</v>
       </c>
       <c r="C10" t="s">
-        <v>15290</v>
+        <v>15335</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -46170,10 +47898,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15290</v>
+        <v>15307</v>
       </c>
       <c r="C11" t="s">
-        <v>15290</v>
+        <v>15336</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -46190,10 +47918,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15290</v>
+        <v>15308</v>
       </c>
       <c r="C12" t="s">
-        <v>15290</v>
+        <v>15337</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -46210,10 +47938,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15290</v>
+        <v>15309</v>
       </c>
       <c r="C13" t="s">
-        <v>15290</v>
+        <v>15338</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -46230,10 +47958,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15290</v>
+        <v>15310</v>
       </c>
       <c r="C14" t="s">
-        <v>15290</v>
+        <v>15339</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -46250,10 +47978,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15290</v>
+        <v>15311</v>
       </c>
       <c r="C15" t="s">
-        <v>15290</v>
+        <v>15340</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -46270,10 +47998,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15290</v>
+        <v>15312</v>
       </c>
       <c r="C16" t="s">
-        <v>15290</v>
+        <v>15341</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -46290,10 +48018,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15290</v>
+        <v>15313</v>
       </c>
       <c r="C17" t="s">
-        <v>15290</v>
+        <v>15342</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -46310,10 +48038,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15290</v>
+        <v>15314</v>
       </c>
       <c r="C18" t="s">
-        <v>15290</v>
+        <v>15343</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -46330,10 +48058,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15290</v>
+        <v>15315</v>
       </c>
       <c r="C19" t="s">
-        <v>15290</v>
+        <v>15344</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -46350,10 +48078,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15290</v>
+        <v>15316</v>
       </c>
       <c r="C20" t="s">
-        <v>15290</v>
+        <v>15345</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -46370,10 +48098,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15290</v>
+        <v>15317</v>
       </c>
       <c r="C21" t="s">
-        <v>15290</v>
+        <v>15346</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -46390,10 +48118,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15290</v>
+        <v>15318</v>
       </c>
       <c r="C22" t="s">
-        <v>15290</v>
+        <v>15347</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -46410,10 +48138,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15290</v>
+        <v>15319</v>
       </c>
       <c r="C23" t="s">
-        <v>15290</v>
+        <v>15348</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -46430,10 +48158,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15290</v>
+        <v>15320</v>
       </c>
       <c r="C24" t="s">
-        <v>15290</v>
+        <v>15349</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -46450,10 +48178,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15290</v>
+        <v>15321</v>
       </c>
       <c r="C25" t="s">
-        <v>15290</v>
+        <v>15350</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -46470,10 +48198,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15290</v>
+        <v>15322</v>
       </c>
       <c r="C26" t="s">
-        <v>15290</v>
+        <v>15351</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -46490,10 +48218,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15290</v>
+        <v>15323</v>
       </c>
       <c r="C27" t="s">
-        <v>15290</v>
+        <v>15352</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -46510,10 +48238,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15290</v>
+        <v>15324</v>
       </c>
       <c r="C28" t="s">
-        <v>15290</v>
+        <v>15353</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -46530,10 +48258,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15290</v>
+        <v>15325</v>
       </c>
       <c r="C29" t="s">
-        <v>15290</v>
+        <v>15354</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -46558,28 +48286,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15232</v>
+        <v>15360</v>
       </c>
       <c r="B1" t="s">
-        <v>15233</v>
+        <v>15361</v>
       </c>
       <c r="C1" t="s">
-        <v>15262</v>
+        <v>15390</v>
       </c>
       <c r="D1" t="s">
-        <v>15291</v>
+        <v>15419</v>
       </c>
       <c r="E1" t="s">
-        <v>15292</v>
+        <v>15420</v>
       </c>
       <c r="F1" t="s">
-        <v>15293</v>
+        <v>15421</v>
       </c>
       <c r="G1" t="s">
-        <v>15294</v>
+        <v>15422</v>
       </c>
       <c r="H1" t="s">
-        <v>15295</v>
+        <v>15423</v>
       </c>
     </row>
     <row r="2">
@@ -46587,10 +48315,10 @@
         <v>2013</v>
       </c>
       <c r="B2" t="s">
-        <v>15234</v>
+        <v>15362</v>
       </c>
       <c r="C2" t="s">
-        <v>15263</v>
+        <v>15391</v>
       </c>
       <c r="D2">
         <v>10193833</v>
@@ -46611,10 +48339,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15290</v>
+        <v>15363</v>
       </c>
       <c r="C3" t="s">
-        <v>15290</v>
+        <v>15392</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -46631,10 +48359,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15290</v>
+        <v>15364</v>
       </c>
       <c r="C4" t="s">
-        <v>15290</v>
+        <v>15393</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -46651,10 +48379,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15290</v>
+        <v>15365</v>
       </c>
       <c r="C5" t="s">
-        <v>15290</v>
+        <v>15394</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -46671,10 +48399,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15290</v>
+        <v>15366</v>
       </c>
       <c r="C6" t="s">
-        <v>15290</v>
+        <v>15395</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -46691,10 +48419,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15290</v>
+        <v>15367</v>
       </c>
       <c r="C7" t="s">
-        <v>15290</v>
+        <v>15396</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -46711,10 +48439,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15290</v>
+        <v>15368</v>
       </c>
       <c r="C8" t="s">
-        <v>15290</v>
+        <v>15397</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -46731,10 +48459,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15290</v>
+        <v>15369</v>
       </c>
       <c r="C9" t="s">
-        <v>15290</v>
+        <v>15398</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -46751,10 +48479,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15290</v>
+        <v>15370</v>
       </c>
       <c r="C10" t="s">
-        <v>15290</v>
+        <v>15399</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -46771,10 +48499,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15290</v>
+        <v>15371</v>
       </c>
       <c r="C11" t="s">
-        <v>15290</v>
+        <v>15400</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -46791,10 +48519,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15290</v>
+        <v>15372</v>
       </c>
       <c r="C12" t="s">
-        <v>15290</v>
+        <v>15401</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -46811,10 +48539,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15290</v>
+        <v>15373</v>
       </c>
       <c r="C13" t="s">
-        <v>15290</v>
+        <v>15402</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -46831,10 +48559,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15290</v>
+        <v>15374</v>
       </c>
       <c r="C14" t="s">
-        <v>15290</v>
+        <v>15403</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -46851,10 +48579,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15290</v>
+        <v>15375</v>
       </c>
       <c r="C15" t="s">
-        <v>15290</v>
+        <v>15404</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -46871,10 +48599,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15290</v>
+        <v>15376</v>
       </c>
       <c r="C16" t="s">
-        <v>15290</v>
+        <v>15405</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -46891,10 +48619,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15290</v>
+        <v>15377</v>
       </c>
       <c r="C17" t="s">
-        <v>15290</v>
+        <v>15406</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -46911,10 +48639,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15290</v>
+        <v>15378</v>
       </c>
       <c r="C18" t="s">
-        <v>15290</v>
+        <v>15407</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -46931,10 +48659,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15290</v>
+        <v>15379</v>
       </c>
       <c r="C19" t="s">
-        <v>15290</v>
+        <v>15408</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -46951,10 +48679,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15290</v>
+        <v>15380</v>
       </c>
       <c r="C20" t="s">
-        <v>15290</v>
+        <v>15409</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -46971,10 +48699,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15290</v>
+        <v>15381</v>
       </c>
       <c r="C21" t="s">
-        <v>15290</v>
+        <v>15410</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -46991,10 +48719,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15290</v>
+        <v>15382</v>
       </c>
       <c r="C22" t="s">
-        <v>15290</v>
+        <v>15411</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -47011,10 +48739,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15290</v>
+        <v>15383</v>
       </c>
       <c r="C23" t="s">
-        <v>15290</v>
+        <v>15412</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -47031,10 +48759,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15290</v>
+        <v>15384</v>
       </c>
       <c r="C24" t="s">
-        <v>15290</v>
+        <v>15413</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -47051,10 +48779,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15290</v>
+        <v>15385</v>
       </c>
       <c r="C25" t="s">
-        <v>15290</v>
+        <v>15414</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -47071,10 +48799,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15290</v>
+        <v>15386</v>
       </c>
       <c r="C26" t="s">
-        <v>15290</v>
+        <v>15415</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -47091,10 +48819,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15290</v>
+        <v>15387</v>
       </c>
       <c r="C27" t="s">
-        <v>15290</v>
+        <v>15416</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -47111,10 +48839,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15290</v>
+        <v>15388</v>
       </c>
       <c r="C28" t="s">
-        <v>15290</v>
+        <v>15417</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -47131,10 +48859,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15290</v>
+        <v>15389</v>
       </c>
       <c r="C29" t="s">
-        <v>15290</v>
+        <v>15418</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -47159,28 +48887,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15232</v>
+        <v>15424</v>
       </c>
       <c r="B1" t="s">
-        <v>15233</v>
+        <v>15425</v>
       </c>
       <c r="C1" t="s">
-        <v>15262</v>
+        <v>15454</v>
       </c>
       <c r="D1" t="s">
-        <v>15291</v>
+        <v>15483</v>
       </c>
       <c r="E1" t="s">
-        <v>15292</v>
+        <v>15484</v>
       </c>
       <c r="F1" t="s">
-        <v>15293</v>
+        <v>15485</v>
       </c>
       <c r="G1" t="s">
-        <v>15294</v>
+        <v>15486</v>
       </c>
       <c r="H1" t="s">
-        <v>15295</v>
+        <v>15487</v>
       </c>
     </row>
     <row r="2">
@@ -47188,10 +48916,10 @@
         <v>2014</v>
       </c>
       <c r="B2" t="s">
-        <v>15234</v>
+        <v>15426</v>
       </c>
       <c r="C2" t="s">
-        <v>15263</v>
+        <v>15455</v>
       </c>
       <c r="D2">
         <v>10315528</v>
@@ -47212,10 +48940,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15290</v>
+        <v>15427</v>
       </c>
       <c r="C3" t="s">
-        <v>15290</v>
+        <v>15456</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -47232,10 +48960,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15290</v>
+        <v>15428</v>
       </c>
       <c r="C4" t="s">
-        <v>15290</v>
+        <v>15457</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -47252,10 +48980,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15290</v>
+        <v>15429</v>
       </c>
       <c r="C5" t="s">
-        <v>15290</v>
+        <v>15458</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -47272,10 +49000,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15290</v>
+        <v>15430</v>
       </c>
       <c r="C6" t="s">
-        <v>15290</v>
+        <v>15459</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -47292,10 +49020,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15290</v>
+        <v>15431</v>
       </c>
       <c r="C7" t="s">
-        <v>15290</v>
+        <v>15460</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -47312,10 +49040,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15290</v>
+        <v>15432</v>
       </c>
       <c r="C8" t="s">
-        <v>15290</v>
+        <v>15461</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -47332,10 +49060,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15290</v>
+        <v>15433</v>
       </c>
       <c r="C9" t="s">
-        <v>15290</v>
+        <v>15462</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -47352,10 +49080,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15290</v>
+        <v>15434</v>
       </c>
       <c r="C10" t="s">
-        <v>15290</v>
+        <v>15463</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -47372,10 +49100,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15290</v>
+        <v>15435</v>
       </c>
       <c r="C11" t="s">
-        <v>15290</v>
+        <v>15464</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -47392,10 +49120,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15290</v>
+        <v>15436</v>
       </c>
       <c r="C12" t="s">
-        <v>15290</v>
+        <v>15465</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -47412,10 +49140,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15290</v>
+        <v>15437</v>
       </c>
       <c r="C13" t="s">
-        <v>15290</v>
+        <v>15466</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -47432,10 +49160,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15290</v>
+        <v>15438</v>
       </c>
       <c r="C14" t="s">
-        <v>15290</v>
+        <v>15467</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -47452,10 +49180,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15290</v>
+        <v>15439</v>
       </c>
       <c r="C15" t="s">
-        <v>15290</v>
+        <v>15468</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -47472,10 +49200,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15290</v>
+        <v>15440</v>
       </c>
       <c r="C16" t="s">
-        <v>15290</v>
+        <v>15469</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -47492,10 +49220,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15290</v>
+        <v>15441</v>
       </c>
       <c r="C17" t="s">
-        <v>15290</v>
+        <v>15470</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -47512,10 +49240,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15290</v>
+        <v>15442</v>
       </c>
       <c r="C18" t="s">
-        <v>15290</v>
+        <v>15471</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -47532,10 +49260,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15290</v>
+        <v>15443</v>
       </c>
       <c r="C19" t="s">
-        <v>15290</v>
+        <v>15472</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -47552,10 +49280,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15290</v>
+        <v>15444</v>
       </c>
       <c r="C20" t="s">
-        <v>15290</v>
+        <v>15473</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -47572,10 +49300,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15290</v>
+        <v>15445</v>
       </c>
       <c r="C21" t="s">
-        <v>15290</v>
+        <v>15474</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -47592,10 +49320,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15290</v>
+        <v>15446</v>
       </c>
       <c r="C22" t="s">
-        <v>15290</v>
+        <v>15475</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -47612,10 +49340,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15290</v>
+        <v>15447</v>
       </c>
       <c r="C23" t="s">
-        <v>15290</v>
+        <v>15476</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -47632,10 +49360,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15290</v>
+        <v>15448</v>
       </c>
       <c r="C24" t="s">
-        <v>15290</v>
+        <v>15477</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -47652,10 +49380,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15290</v>
+        <v>15449</v>
       </c>
       <c r="C25" t="s">
-        <v>15290</v>
+        <v>15478</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -47672,10 +49400,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15290</v>
+        <v>15450</v>
       </c>
       <c r="C26" t="s">
-        <v>15290</v>
+        <v>15479</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -47692,10 +49420,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15290</v>
+        <v>15451</v>
       </c>
       <c r="C27" t="s">
-        <v>15290</v>
+        <v>15480</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -47712,10 +49440,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15290</v>
+        <v>15452</v>
       </c>
       <c r="C28" t="s">
-        <v>15290</v>
+        <v>15481</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -47732,10 +49460,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15290</v>
+        <v>15453</v>
       </c>
       <c r="C29" t="s">
-        <v>15290</v>
+        <v>15482</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -47760,28 +49488,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15232</v>
+        <v>15488</v>
       </c>
       <c r="B1" t="s">
-        <v>15233</v>
+        <v>15489</v>
       </c>
       <c r="C1" t="s">
-        <v>15262</v>
+        <v>15518</v>
       </c>
       <c r="D1" t="s">
-        <v>15291</v>
+        <v>15547</v>
       </c>
       <c r="E1" t="s">
-        <v>15292</v>
+        <v>15548</v>
       </c>
       <c r="F1" t="s">
-        <v>15293</v>
+        <v>15549</v>
       </c>
       <c r="G1" t="s">
-        <v>15294</v>
+        <v>15550</v>
       </c>
       <c r="H1" t="s">
-        <v>15295</v>
+        <v>15551</v>
       </c>
     </row>
     <row r="2">
@@ -47789,10 +49517,10 @@
         <v>2015</v>
       </c>
       <c r="B2" t="s">
-        <v>15234</v>
+        <v>15490</v>
       </c>
       <c r="C2" t="s">
-        <v>15263</v>
+        <v>15519</v>
       </c>
       <c r="D2">
         <v>10434829</v>
@@ -47813,10 +49541,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15290</v>
+        <v>15491</v>
       </c>
       <c r="C3" t="s">
-        <v>15290</v>
+        <v>15520</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -47833,10 +49561,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15290</v>
+        <v>15492</v>
       </c>
       <c r="C4" t="s">
-        <v>15290</v>
+        <v>15521</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -47853,10 +49581,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15290</v>
+        <v>15493</v>
       </c>
       <c r="C5" t="s">
-        <v>15290</v>
+        <v>15522</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -47873,10 +49601,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15290</v>
+        <v>15494</v>
       </c>
       <c r="C6" t="s">
-        <v>15290</v>
+        <v>15523</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -47893,10 +49621,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15290</v>
+        <v>15495</v>
       </c>
       <c r="C7" t="s">
-        <v>15290</v>
+        <v>15524</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -47913,10 +49641,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15290</v>
+        <v>15496</v>
       </c>
       <c r="C8" t="s">
-        <v>15290</v>
+        <v>15525</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -47933,10 +49661,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15290</v>
+        <v>15497</v>
       </c>
       <c r="C9" t="s">
-        <v>15290</v>
+        <v>15526</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -47953,10 +49681,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15290</v>
+        <v>15498</v>
       </c>
       <c r="C10" t="s">
-        <v>15290</v>
+        <v>15527</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -47973,10 +49701,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15290</v>
+        <v>15499</v>
       </c>
       <c r="C11" t="s">
-        <v>15290</v>
+        <v>15528</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -47993,10 +49721,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15290</v>
+        <v>15500</v>
       </c>
       <c r="C12" t="s">
-        <v>15290</v>
+        <v>15529</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -48013,10 +49741,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15290</v>
+        <v>15501</v>
       </c>
       <c r="C13" t="s">
-        <v>15290</v>
+        <v>15530</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -48033,10 +49761,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15290</v>
+        <v>15502</v>
       </c>
       <c r="C14" t="s">
-        <v>15290</v>
+        <v>15531</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -48053,10 +49781,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15290</v>
+        <v>15503</v>
       </c>
       <c r="C15" t="s">
-        <v>15290</v>
+        <v>15532</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -48073,10 +49801,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15290</v>
+        <v>15504</v>
       </c>
       <c r="C16" t="s">
-        <v>15290</v>
+        <v>15533</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -48093,10 +49821,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15290</v>
+        <v>15505</v>
       </c>
       <c r="C17" t="s">
-        <v>15290</v>
+        <v>15534</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -48113,10 +49841,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15290</v>
+        <v>15506</v>
       </c>
       <c r="C18" t="s">
-        <v>15290</v>
+        <v>15535</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -48133,10 +49861,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15290</v>
+        <v>15507</v>
       </c>
       <c r="C19" t="s">
-        <v>15290</v>
+        <v>15536</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -48153,10 +49881,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15290</v>
+        <v>15508</v>
       </c>
       <c r="C20" t="s">
-        <v>15290</v>
+        <v>15537</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -48173,10 +49901,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15290</v>
+        <v>15509</v>
       </c>
       <c r="C21" t="s">
-        <v>15290</v>
+        <v>15538</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -48193,10 +49921,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15290</v>
+        <v>15510</v>
       </c>
       <c r="C22" t="s">
-        <v>15290</v>
+        <v>15539</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -48213,10 +49941,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15290</v>
+        <v>15511</v>
       </c>
       <c r="C23" t="s">
-        <v>15290</v>
+        <v>15540</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -48233,10 +49961,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15290</v>
+        <v>15512</v>
       </c>
       <c r="C24" t="s">
-        <v>15290</v>
+        <v>15541</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -48253,10 +49981,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15290</v>
+        <v>15513</v>
       </c>
       <c r="C25" t="s">
-        <v>15290</v>
+        <v>15542</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -48273,10 +50001,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15290</v>
+        <v>15514</v>
       </c>
       <c r="C26" t="s">
-        <v>15290</v>
+        <v>15543</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -48293,10 +50021,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15290</v>
+        <v>15515</v>
       </c>
       <c r="C27" t="s">
-        <v>15290</v>
+        <v>15544</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -48313,10 +50041,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15290</v>
+        <v>15516</v>
       </c>
       <c r="C28" t="s">
-        <v>15290</v>
+        <v>15545</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -48333,10 +50061,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15290</v>
+        <v>15517</v>
       </c>
       <c r="C29" t="s">
-        <v>15290</v>
+        <v>15546</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -48361,28 +50089,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15232</v>
+        <v>15552</v>
       </c>
       <c r="B1" t="s">
-        <v>15233</v>
+        <v>15553</v>
       </c>
       <c r="C1" t="s">
-        <v>15262</v>
+        <v>15582</v>
       </c>
       <c r="D1" t="s">
-        <v>15291</v>
+        <v>15611</v>
       </c>
       <c r="E1" t="s">
-        <v>15292</v>
+        <v>15612</v>
       </c>
       <c r="F1" t="s">
-        <v>15293</v>
+        <v>15613</v>
       </c>
       <c r="G1" t="s">
-        <v>15294</v>
+        <v>15614</v>
       </c>
       <c r="H1" t="s">
-        <v>15295</v>
+        <v>15615</v>
       </c>
     </row>
     <row r="2">
@@ -48390,10 +50118,10 @@
         <v>2016</v>
       </c>
       <c r="B2" t="s">
-        <v>15234</v>
+        <v>15554</v>
       </c>
       <c r="C2" t="s">
-        <v>15263</v>
+        <v>15583</v>
       </c>
       <c r="D2">
         <v>10551430</v>
@@ -48414,10 +50142,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15290</v>
+        <v>15555</v>
       </c>
       <c r="C3" t="s">
-        <v>15290</v>
+        <v>15584</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -48434,10 +50162,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15290</v>
+        <v>15556</v>
       </c>
       <c r="C4" t="s">
-        <v>15290</v>
+        <v>15585</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -48454,10 +50182,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15290</v>
+        <v>15557</v>
       </c>
       <c r="C5" t="s">
-        <v>15290</v>
+        <v>15586</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -48474,10 +50202,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15290</v>
+        <v>15558</v>
       </c>
       <c r="C6" t="s">
-        <v>15290</v>
+        <v>15587</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -48494,10 +50222,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15290</v>
+        <v>15559</v>
       </c>
       <c r="C7" t="s">
-        <v>15290</v>
+        <v>15588</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -48514,10 +50242,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15290</v>
+        <v>15560</v>
       </c>
       <c r="C8" t="s">
-        <v>15290</v>
+        <v>15589</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -48534,10 +50262,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15290</v>
+        <v>15561</v>
       </c>
       <c r="C9" t="s">
-        <v>15290</v>
+        <v>15590</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -48554,10 +50282,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15290</v>
+        <v>15562</v>
       </c>
       <c r="C10" t="s">
-        <v>15290</v>
+        <v>15591</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -48574,10 +50302,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15290</v>
+        <v>15563</v>
       </c>
       <c r="C11" t="s">
-        <v>15290</v>
+        <v>15592</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -48594,10 +50322,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15290</v>
+        <v>15564</v>
       </c>
       <c r="C12" t="s">
-        <v>15290</v>
+        <v>15593</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -48614,10 +50342,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15290</v>
+        <v>15565</v>
       </c>
       <c r="C13" t="s">
-        <v>15290</v>
+        <v>15594</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -48634,10 +50362,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15290</v>
+        <v>15566</v>
       </c>
       <c r="C14" t="s">
-        <v>15290</v>
+        <v>15595</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -48654,10 +50382,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15290</v>
+        <v>15567</v>
       </c>
       <c r="C15" t="s">
-        <v>15290</v>
+        <v>15596</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -48674,10 +50402,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15290</v>
+        <v>15568</v>
       </c>
       <c r="C16" t="s">
-        <v>15290</v>
+        <v>15597</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -48694,10 +50422,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15290</v>
+        <v>15569</v>
       </c>
       <c r="C17" t="s">
-        <v>15290</v>
+        <v>15598</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -48714,10 +50442,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15290</v>
+        <v>15570</v>
       </c>
       <c r="C18" t="s">
-        <v>15290</v>
+        <v>15599</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -48734,10 +50462,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15290</v>
+        <v>15571</v>
       </c>
       <c r="C19" t="s">
-        <v>15290</v>
+        <v>15600</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -48754,10 +50482,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15290</v>
+        <v>15572</v>
       </c>
       <c r="C20" t="s">
-        <v>15290</v>
+        <v>15601</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -48774,10 +50502,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15290</v>
+        <v>15573</v>
       </c>
       <c r="C21" t="s">
-        <v>15290</v>
+        <v>15602</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -48794,10 +50522,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15290</v>
+        <v>15574</v>
       </c>
       <c r="C22" t="s">
-        <v>15290</v>
+        <v>15603</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -48814,10 +50542,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15290</v>
+        <v>15575</v>
       </c>
       <c r="C23" t="s">
-        <v>15290</v>
+        <v>15604</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -48834,10 +50562,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15290</v>
+        <v>15576</v>
       </c>
       <c r="C24" t="s">
-        <v>15290</v>
+        <v>15605</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -48854,10 +50582,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15290</v>
+        <v>15577</v>
       </c>
       <c r="C25" t="s">
-        <v>15290</v>
+        <v>15606</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -48874,10 +50602,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15290</v>
+        <v>15578</v>
       </c>
       <c r="C26" t="s">
-        <v>15290</v>
+        <v>15607</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -48894,10 +50622,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15290</v>
+        <v>15579</v>
       </c>
       <c r="C27" t="s">
-        <v>15290</v>
+        <v>15608</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -48914,10 +50642,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15290</v>
+        <v>15580</v>
       </c>
       <c r="C28" t="s">
-        <v>15290</v>
+        <v>15609</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -48934,10 +50662,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15290</v>
+        <v>15581</v>
       </c>
       <c r="C29" t="s">
-        <v>15290</v>
+        <v>15610</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -48962,28 +50690,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15232</v>
+        <v>15616</v>
       </c>
       <c r="B1" t="s">
-        <v>15233</v>
+        <v>15617</v>
       </c>
       <c r="C1" t="s">
-        <v>15262</v>
+        <v>15646</v>
       </c>
       <c r="D1" t="s">
-        <v>15291</v>
+        <v>15675</v>
       </c>
       <c r="E1" t="s">
-        <v>15292</v>
+        <v>15676</v>
       </c>
       <c r="F1" t="s">
-        <v>15293</v>
+        <v>15677</v>
       </c>
       <c r="G1" t="s">
-        <v>15294</v>
+        <v>15678</v>
       </c>
       <c r="H1" t="s">
-        <v>15295</v>
+        <v>15679</v>
       </c>
     </row>
     <row r="2">
@@ -48991,10 +50719,10 @@
         <v>2017</v>
       </c>
       <c r="B2" t="s">
-        <v>15234</v>
+        <v>15618</v>
       </c>
       <c r="C2" t="s">
-        <v>15263</v>
+        <v>15647</v>
       </c>
       <c r="D2">
         <v>10666843</v>
@@ -49015,10 +50743,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15290</v>
+        <v>15619</v>
       </c>
       <c r="C3" t="s">
-        <v>15290</v>
+        <v>15648</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -49035,10 +50763,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15290</v>
+        <v>15620</v>
       </c>
       <c r="C4" t="s">
-        <v>15290</v>
+        <v>15649</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -49055,10 +50783,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15290</v>
+        <v>15621</v>
       </c>
       <c r="C5" t="s">
-        <v>15290</v>
+        <v>15650</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -49075,10 +50803,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15290</v>
+        <v>15622</v>
       </c>
       <c r="C6" t="s">
-        <v>15290</v>
+        <v>15651</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -49095,10 +50823,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15290</v>
+        <v>15623</v>
       </c>
       <c r="C7" t="s">
-        <v>15290</v>
+        <v>15652</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -49115,10 +50843,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15290</v>
+        <v>15624</v>
       </c>
       <c r="C8" t="s">
-        <v>15290</v>
+        <v>15653</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -49135,10 +50863,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15290</v>
+        <v>15625</v>
       </c>
       <c r="C9" t="s">
-        <v>15290</v>
+        <v>15654</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -49155,10 +50883,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15290</v>
+        <v>15626</v>
       </c>
       <c r="C10" t="s">
-        <v>15290</v>
+        <v>15655</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -49175,10 +50903,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15290</v>
+        <v>15627</v>
       </c>
       <c r="C11" t="s">
-        <v>15290</v>
+        <v>15656</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -49195,10 +50923,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15290</v>
+        <v>15628</v>
       </c>
       <c r="C12" t="s">
-        <v>15290</v>
+        <v>15657</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -49215,10 +50943,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15290</v>
+        <v>15629</v>
       </c>
       <c r="C13" t="s">
-        <v>15290</v>
+        <v>15658</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -49235,10 +50963,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15290</v>
+        <v>15630</v>
       </c>
       <c r="C14" t="s">
-        <v>15290</v>
+        <v>15659</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -49255,10 +50983,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15290</v>
+        <v>15631</v>
       </c>
       <c r="C15" t="s">
-        <v>15290</v>
+        <v>15660</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -49275,10 +51003,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15290</v>
+        <v>15632</v>
       </c>
       <c r="C16" t="s">
-        <v>15290</v>
+        <v>15661</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -49295,10 +51023,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15290</v>
+        <v>15633</v>
       </c>
       <c r="C17" t="s">
-        <v>15290</v>
+        <v>15662</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -49315,10 +51043,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15290</v>
+        <v>15634</v>
       </c>
       <c r="C18" t="s">
-        <v>15290</v>
+        <v>15663</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -49335,10 +51063,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15290</v>
+        <v>15635</v>
       </c>
       <c r="C19" t="s">
-        <v>15290</v>
+        <v>15664</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -49355,10 +51083,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15290</v>
+        <v>15636</v>
       </c>
       <c r="C20" t="s">
-        <v>15290</v>
+        <v>15665</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -49375,10 +51103,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15290</v>
+        <v>15637</v>
       </c>
       <c r="C21" t="s">
-        <v>15290</v>
+        <v>15666</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -49395,10 +51123,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15290</v>
+        <v>15638</v>
       </c>
       <c r="C22" t="s">
-        <v>15290</v>
+        <v>15667</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -49415,10 +51143,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15290</v>
+        <v>15639</v>
       </c>
       <c r="C23" t="s">
-        <v>15290</v>
+        <v>15668</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -49435,10 +51163,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15290</v>
+        <v>15640</v>
       </c>
       <c r="C24" t="s">
-        <v>15290</v>
+        <v>15669</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -49455,10 +51183,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15290</v>
+        <v>15641</v>
       </c>
       <c r="C25" t="s">
-        <v>15290</v>
+        <v>15670</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -49475,10 +51203,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15290</v>
+        <v>15642</v>
       </c>
       <c r="C26" t="s">
-        <v>15290</v>
+        <v>15671</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -49495,10 +51223,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15290</v>
+        <v>15643</v>
       </c>
       <c r="C27" t="s">
-        <v>15290</v>
+        <v>15672</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -49515,10 +51243,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15290</v>
+        <v>15644</v>
       </c>
       <c r="C28" t="s">
-        <v>15290</v>
+        <v>15673</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -49535,10 +51263,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15290</v>
+        <v>15645</v>
       </c>
       <c r="C29" t="s">
-        <v>15290</v>
+        <v>15674</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -49563,28 +51291,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15232</v>
+        <v>15680</v>
       </c>
       <c r="B1" t="s">
-        <v>15233</v>
+        <v>15681</v>
       </c>
       <c r="C1" t="s">
-        <v>15262</v>
+        <v>15710</v>
       </c>
       <c r="D1" t="s">
-        <v>15291</v>
+        <v>15739</v>
       </c>
       <c r="E1" t="s">
-        <v>15292</v>
+        <v>15740</v>
       </c>
       <c r="F1" t="s">
-        <v>15293</v>
+        <v>15741</v>
       </c>
       <c r="G1" t="s">
-        <v>15294</v>
+        <v>15742</v>
       </c>
       <c r="H1" t="s">
-        <v>15295</v>
+        <v>15743</v>
       </c>
     </row>
     <row r="2">
@@ -49592,10 +51320,10 @@
         <v>2018</v>
       </c>
       <c r="B2" t="s">
-        <v>15234</v>
+        <v>15682</v>
       </c>
       <c r="C2" t="s">
-        <v>15263</v>
+        <v>15711</v>
       </c>
       <c r="D2">
         <v>10782053</v>
@@ -49616,10 +51344,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15290</v>
+        <v>15683</v>
       </c>
       <c r="C3" t="s">
-        <v>15290</v>
+        <v>15712</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -49636,10 +51364,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15290</v>
+        <v>15684</v>
       </c>
       <c r="C4" t="s">
-        <v>15290</v>
+        <v>15713</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -49656,10 +51384,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15290</v>
+        <v>15685</v>
       </c>
       <c r="C5" t="s">
-        <v>15290</v>
+        <v>15714</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -49676,10 +51404,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15290</v>
+        <v>15686</v>
       </c>
       <c r="C6" t="s">
-        <v>15290</v>
+        <v>15715</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -49696,10 +51424,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15290</v>
+        <v>15687</v>
       </c>
       <c r="C7" t="s">
-        <v>15290</v>
+        <v>15716</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -49716,10 +51444,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15290</v>
+        <v>15688</v>
       </c>
       <c r="C8" t="s">
-        <v>15290</v>
+        <v>15717</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -49736,10 +51464,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15290</v>
+        <v>15689</v>
       </c>
       <c r="C9" t="s">
-        <v>15290</v>
+        <v>15718</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -49756,10 +51484,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15290</v>
+        <v>15690</v>
       </c>
       <c r="C10" t="s">
-        <v>15290</v>
+        <v>15719</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -49776,10 +51504,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15290</v>
+        <v>15691</v>
       </c>
       <c r="C11" t="s">
-        <v>15290</v>
+        <v>15720</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -49796,10 +51524,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15290</v>
+        <v>15692</v>
       </c>
       <c r="C12" t="s">
-        <v>15290</v>
+        <v>15721</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -49816,10 +51544,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15290</v>
+        <v>15693</v>
       </c>
       <c r="C13" t="s">
-        <v>15290</v>
+        <v>15722</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -49836,10 +51564,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15290</v>
+        <v>15694</v>
       </c>
       <c r="C14" t="s">
-        <v>15290</v>
+        <v>15723</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -49856,10 +51584,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15290</v>
+        <v>15695</v>
       </c>
       <c r="C15" t="s">
-        <v>15290</v>
+        <v>15724</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -49876,10 +51604,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15290</v>
+        <v>15696</v>
       </c>
       <c r="C16" t="s">
-        <v>15290</v>
+        <v>15725</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -49896,10 +51624,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15290</v>
+        <v>15697</v>
       </c>
       <c r="C17" t="s">
-        <v>15290</v>
+        <v>15726</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -49916,10 +51644,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15290</v>
+        <v>15698</v>
       </c>
       <c r="C18" t="s">
-        <v>15290</v>
+        <v>15727</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -49936,10 +51664,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15290</v>
+        <v>15699</v>
       </c>
       <c r="C19" t="s">
-        <v>15290</v>
+        <v>15728</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -49956,10 +51684,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15290</v>
+        <v>15700</v>
       </c>
       <c r="C20" t="s">
-        <v>15290</v>
+        <v>15729</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -49976,10 +51704,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15290</v>
+        <v>15701</v>
       </c>
       <c r="C21" t="s">
-        <v>15290</v>
+        <v>15730</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -49996,10 +51724,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15290</v>
+        <v>15702</v>
       </c>
       <c r="C22" t="s">
-        <v>15290</v>
+        <v>15731</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -50016,10 +51744,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15290</v>
+        <v>15703</v>
       </c>
       <c r="C23" t="s">
-        <v>15290</v>
+        <v>15732</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -50036,10 +51764,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15290</v>
+        <v>15704</v>
       </c>
       <c r="C24" t="s">
-        <v>15290</v>
+        <v>15733</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -50056,10 +51784,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15290</v>
+        <v>15705</v>
       </c>
       <c r="C25" t="s">
-        <v>15290</v>
+        <v>15734</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -50076,10 +51804,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15290</v>
+        <v>15706</v>
       </c>
       <c r="C26" t="s">
-        <v>15290</v>
+        <v>15735</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -50096,10 +51824,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15290</v>
+        <v>15707</v>
       </c>
       <c r="C27" t="s">
-        <v>15290</v>
+        <v>15736</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -50116,10 +51844,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15290</v>
+        <v>15708</v>
       </c>
       <c r="C28" t="s">
-        <v>15290</v>
+        <v>15737</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -50136,10 +51864,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15290</v>
+        <v>15709</v>
       </c>
       <c r="C29" t="s">
-        <v>15290</v>
+        <v>15738</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -50164,28 +51892,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15232</v>
+        <v>15744</v>
       </c>
       <c r="B1" t="s">
-        <v>15233</v>
+        <v>15745</v>
       </c>
       <c r="C1" t="s">
-        <v>15262</v>
+        <v>15774</v>
       </c>
       <c r="D1" t="s">
-        <v>15291</v>
+        <v>15803</v>
       </c>
       <c r="E1" t="s">
-        <v>15292</v>
+        <v>15804</v>
       </c>
       <c r="F1" t="s">
-        <v>15293</v>
+        <v>15805</v>
       </c>
       <c r="G1" t="s">
-        <v>15294</v>
+        <v>15806</v>
       </c>
       <c r="H1" t="s">
-        <v>15295</v>
+        <v>15807</v>
       </c>
     </row>
     <row r="2">
@@ -50193,10 +51921,10 @@
         <v>2019</v>
       </c>
       <c r="B2" t="s">
-        <v>15234</v>
+        <v>15746</v>
       </c>
       <c r="C2" t="s">
-        <v>15263</v>
+        <v>15775</v>
       </c>
       <c r="D2">
         <v>10894043</v>
@@ -50217,10 +51945,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15290</v>
+        <v>15747</v>
       </c>
       <c r="C3" t="s">
-        <v>15290</v>
+        <v>15776</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -50237,10 +51965,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15290</v>
+        <v>15748</v>
       </c>
       <c r="C4" t="s">
-        <v>15290</v>
+        <v>15777</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -50257,10 +51985,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15290</v>
+        <v>15749</v>
       </c>
       <c r="C5" t="s">
-        <v>15290</v>
+        <v>15778</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -50277,10 +52005,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15290</v>
+        <v>15750</v>
       </c>
       <c r="C6" t="s">
-        <v>15290</v>
+        <v>15779</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -50297,10 +52025,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15290</v>
+        <v>15751</v>
       </c>
       <c r="C7" t="s">
-        <v>15290</v>
+        <v>15780</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -50317,10 +52045,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15290</v>
+        <v>15752</v>
       </c>
       <c r="C8" t="s">
-        <v>15290</v>
+        <v>15781</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -50337,10 +52065,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15290</v>
+        <v>15753</v>
       </c>
       <c r="C9" t="s">
-        <v>15290</v>
+        <v>15782</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -50357,10 +52085,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15290</v>
+        <v>15754</v>
       </c>
       <c r="C10" t="s">
-        <v>15290</v>
+        <v>15783</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -50377,10 +52105,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15290</v>
+        <v>15755</v>
       </c>
       <c r="C11" t="s">
-        <v>15290</v>
+        <v>15784</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -50397,10 +52125,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15290</v>
+        <v>15756</v>
       </c>
       <c r="C12" t="s">
-        <v>15290</v>
+        <v>15785</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -50417,10 +52145,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15290</v>
+        <v>15757</v>
       </c>
       <c r="C13" t="s">
-        <v>15290</v>
+        <v>15786</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -50437,10 +52165,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15290</v>
+        <v>15758</v>
       </c>
       <c r="C14" t="s">
-        <v>15290</v>
+        <v>15787</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -50457,10 +52185,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15290</v>
+        <v>15759</v>
       </c>
       <c r="C15" t="s">
-        <v>15290</v>
+        <v>15788</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -50477,10 +52205,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15290</v>
+        <v>15760</v>
       </c>
       <c r="C16" t="s">
-        <v>15290</v>
+        <v>15789</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -50497,10 +52225,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15290</v>
+        <v>15761</v>
       </c>
       <c r="C17" t="s">
-        <v>15290</v>
+        <v>15790</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -50517,10 +52245,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15290</v>
+        <v>15762</v>
       </c>
       <c r="C18" t="s">
-        <v>15290</v>
+        <v>15791</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -50537,10 +52265,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15290</v>
+        <v>15763</v>
       </c>
       <c r="C19" t="s">
-        <v>15290</v>
+        <v>15792</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -50557,10 +52285,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15290</v>
+        <v>15764</v>
       </c>
       <c r="C20" t="s">
-        <v>15290</v>
+        <v>15793</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -50577,10 +52305,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15290</v>
+        <v>15765</v>
       </c>
       <c r="C21" t="s">
-        <v>15290</v>
+        <v>15794</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -50597,10 +52325,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15290</v>
+        <v>15766</v>
       </c>
       <c r="C22" t="s">
-        <v>15290</v>
+        <v>15795</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -50617,10 +52345,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15290</v>
+        <v>15767</v>
       </c>
       <c r="C23" t="s">
-        <v>15290</v>
+        <v>15796</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -50637,10 +52365,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15290</v>
+        <v>15768</v>
       </c>
       <c r="C24" t="s">
-        <v>15290</v>
+        <v>15797</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -50657,10 +52385,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15290</v>
+        <v>15769</v>
       </c>
       <c r="C25" t="s">
-        <v>15290</v>
+        <v>15798</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -50677,10 +52405,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15290</v>
+        <v>15770</v>
       </c>
       <c r="C26" t="s">
-        <v>15290</v>
+        <v>15799</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -50697,10 +52425,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15290</v>
+        <v>15771</v>
       </c>
       <c r="C27" t="s">
-        <v>15290</v>
+        <v>15800</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -50717,10 +52445,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15290</v>
+        <v>15772</v>
       </c>
       <c r="C28" t="s">
-        <v>15290</v>
+        <v>15801</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -50737,10 +52465,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15290</v>
+        <v>15773</v>
       </c>
       <c r="C29" t="s">
-        <v>15290</v>
+        <v>15802</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -50765,28 +52493,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15232</v>
+        <v>15808</v>
       </c>
       <c r="B1" t="s">
-        <v>15233</v>
+        <v>15809</v>
       </c>
       <c r="C1" t="s">
-        <v>15262</v>
+        <v>15838</v>
       </c>
       <c r="D1" t="s">
-        <v>15291</v>
+        <v>15867</v>
       </c>
       <c r="E1" t="s">
-        <v>15292</v>
+        <v>15868</v>
       </c>
       <c r="F1" t="s">
-        <v>15293</v>
+        <v>15869</v>
       </c>
       <c r="G1" t="s">
-        <v>15294</v>
+        <v>15870</v>
       </c>
       <c r="H1" t="s">
-        <v>15295</v>
+        <v>15871</v>
       </c>
     </row>
     <row r="2">
@@ -50794,10 +52522,10 @@
         <v>2020</v>
       </c>
       <c r="B2" t="s">
-        <v>15234</v>
+        <v>15810</v>
       </c>
       <c r="C2" t="s">
-        <v>15263</v>
+        <v>15839</v>
       </c>
       <c r="D2">
         <v>11008300</v>
@@ -50818,10 +52546,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15290</v>
+        <v>15811</v>
       </c>
       <c r="C3" t="s">
-        <v>15290</v>
+        <v>15840</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -50838,10 +52566,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15290</v>
+        <v>15812</v>
       </c>
       <c r="C4" t="s">
-        <v>15290</v>
+        <v>15841</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -50858,10 +52586,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15290</v>
+        <v>15813</v>
       </c>
       <c r="C5" t="s">
-        <v>15290</v>
+        <v>15842</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -50878,10 +52606,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15290</v>
+        <v>15814</v>
       </c>
       <c r="C6" t="s">
-        <v>15290</v>
+        <v>15843</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -50898,10 +52626,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15290</v>
+        <v>15815</v>
       </c>
       <c r="C7" t="s">
-        <v>15290</v>
+        <v>15844</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -50918,10 +52646,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15290</v>
+        <v>15816</v>
       </c>
       <c r="C8" t="s">
-        <v>15290</v>
+        <v>15845</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -50938,10 +52666,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15290</v>
+        <v>15817</v>
       </c>
       <c r="C9" t="s">
-        <v>15290</v>
+        <v>15846</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -50958,10 +52686,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15290</v>
+        <v>15818</v>
       </c>
       <c r="C10" t="s">
-        <v>15290</v>
+        <v>15847</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -50978,10 +52706,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15290</v>
+        <v>15819</v>
       </c>
       <c r="C11" t="s">
-        <v>15290</v>
+        <v>15848</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -50998,10 +52726,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15290</v>
+        <v>15820</v>
       </c>
       <c r="C12" t="s">
-        <v>15290</v>
+        <v>15849</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -51018,10 +52746,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15290</v>
+        <v>15821</v>
       </c>
       <c r="C13" t="s">
-        <v>15290</v>
+        <v>15850</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -51038,10 +52766,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15290</v>
+        <v>15822</v>
       </c>
       <c r="C14" t="s">
-        <v>15290</v>
+        <v>15851</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -51058,10 +52786,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15290</v>
+        <v>15823</v>
       </c>
       <c r="C15" t="s">
-        <v>15290</v>
+        <v>15852</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -51078,10 +52806,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15290</v>
+        <v>15824</v>
       </c>
       <c r="C16" t="s">
-        <v>15290</v>
+        <v>15853</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -51098,10 +52826,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15290</v>
+        <v>15825</v>
       </c>
       <c r="C17" t="s">
-        <v>15290</v>
+        <v>15854</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -51118,10 +52846,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15290</v>
+        <v>15826</v>
       </c>
       <c r="C18" t="s">
-        <v>15290</v>
+        <v>15855</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -51138,10 +52866,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15290</v>
+        <v>15827</v>
       </c>
       <c r="C19" t="s">
-        <v>15290</v>
+        <v>15856</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -51158,10 +52886,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15290</v>
+        <v>15828</v>
       </c>
       <c r="C20" t="s">
-        <v>15290</v>
+        <v>15857</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -51178,10 +52906,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15290</v>
+        <v>15829</v>
       </c>
       <c r="C21" t="s">
-        <v>15290</v>
+        <v>15858</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -51198,10 +52926,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15290</v>
+        <v>15830</v>
       </c>
       <c r="C22" t="s">
-        <v>15290</v>
+        <v>15859</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -51218,10 +52946,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15290</v>
+        <v>15831</v>
       </c>
       <c r="C23" t="s">
-        <v>15290</v>
+        <v>15860</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -51238,10 +52966,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15290</v>
+        <v>15832</v>
       </c>
       <c r="C24" t="s">
-        <v>15290</v>
+        <v>15861</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -51258,10 +52986,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15290</v>
+        <v>15833</v>
       </c>
       <c r="C25" t="s">
-        <v>15290</v>
+        <v>15862</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -51278,10 +53006,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15290</v>
+        <v>15834</v>
       </c>
       <c r="C26" t="s">
-        <v>15290</v>
+        <v>15863</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -51298,10 +53026,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15290</v>
+        <v>15835</v>
       </c>
       <c r="C27" t="s">
-        <v>15290</v>
+        <v>15864</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -51318,10 +53046,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15290</v>
+        <v>15836</v>
       </c>
       <c r="C28" t="s">
-        <v>15290</v>
+        <v>15865</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -51338,10 +53066,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15290</v>
+        <v>15837</v>
       </c>
       <c r="C29" t="s">
-        <v>15290</v>
+        <v>15866</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>

--- a/input_data/admin_data/DOM/_clean/total-pre-DOM.xlsx
+++ b/input_data/admin_data/DOM/_clean/total-pre-DOM.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22208" uniqueCount="15872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22784" uniqueCount="15872">
   <si>
     <t>year</t>
   </si>
@@ -47685,28 +47685,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15296</v>
+        <v>15808</v>
       </c>
       <c r="B1" t="s">
-        <v>15297</v>
+        <v>15809</v>
       </c>
       <c r="C1" t="s">
-        <v>15326</v>
+        <v>15838</v>
       </c>
       <c r="D1" t="s">
-        <v>15355</v>
+        <v>15867</v>
       </c>
       <c r="E1" t="s">
-        <v>15356</v>
+        <v>15868</v>
       </c>
       <c r="F1" t="s">
-        <v>15357</v>
+        <v>15869</v>
       </c>
       <c r="G1" t="s">
-        <v>15358</v>
+        <v>15870</v>
       </c>
       <c r="H1" t="s">
-        <v>15359</v>
+        <v>15871</v>
       </c>
     </row>
     <row r="2">
@@ -47714,10 +47714,10 @@
         <v>2012</v>
       </c>
       <c r="B2" t="s">
-        <v>15298</v>
+        <v>15810</v>
       </c>
       <c r="C2" t="s">
-        <v>15327</v>
+        <v>15839</v>
       </c>
       <c r="D2">
         <v>10070411</v>
@@ -47738,10 +47738,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15299</v>
+        <v>15866</v>
       </c>
       <c r="C3" t="s">
-        <v>15328</v>
+        <v>15866</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -47758,10 +47758,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15300</v>
+        <v>15866</v>
       </c>
       <c r="C4" t="s">
-        <v>15329</v>
+        <v>15866</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -47778,10 +47778,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15301</v>
+        <v>15866</v>
       </c>
       <c r="C5" t="s">
-        <v>15330</v>
+        <v>15866</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -47798,10 +47798,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15302</v>
+        <v>15866</v>
       </c>
       <c r="C6" t="s">
-        <v>15331</v>
+        <v>15866</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -47818,10 +47818,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15303</v>
+        <v>15866</v>
       </c>
       <c r="C7" t="s">
-        <v>15332</v>
+        <v>15866</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -47838,10 +47838,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15304</v>
+        <v>15866</v>
       </c>
       <c r="C8" t="s">
-        <v>15333</v>
+        <v>15866</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -47858,10 +47858,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15305</v>
+        <v>15866</v>
       </c>
       <c r="C9" t="s">
-        <v>15334</v>
+        <v>15866</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -47878,10 +47878,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15306</v>
+        <v>15866</v>
       </c>
       <c r="C10" t="s">
-        <v>15335</v>
+        <v>15866</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -47898,10 +47898,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15307</v>
+        <v>15866</v>
       </c>
       <c r="C11" t="s">
-        <v>15336</v>
+        <v>15866</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -47918,10 +47918,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15308</v>
+        <v>15866</v>
       </c>
       <c r="C12" t="s">
-        <v>15337</v>
+        <v>15866</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -47938,10 +47938,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15309</v>
+        <v>15866</v>
       </c>
       <c r="C13" t="s">
-        <v>15338</v>
+        <v>15866</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -47958,10 +47958,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15310</v>
+        <v>15866</v>
       </c>
       <c r="C14" t="s">
-        <v>15339</v>
+        <v>15866</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -47978,10 +47978,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15311</v>
+        <v>15866</v>
       </c>
       <c r="C15" t="s">
-        <v>15340</v>
+        <v>15866</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -47998,10 +47998,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15312</v>
+        <v>15866</v>
       </c>
       <c r="C16" t="s">
-        <v>15341</v>
+        <v>15866</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -48018,10 +48018,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15313</v>
+        <v>15866</v>
       </c>
       <c r="C17" t="s">
-        <v>15342</v>
+        <v>15866</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -48038,10 +48038,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15314</v>
+        <v>15866</v>
       </c>
       <c r="C18" t="s">
-        <v>15343</v>
+        <v>15866</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -48058,10 +48058,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15315</v>
+        <v>15866</v>
       </c>
       <c r="C19" t="s">
-        <v>15344</v>
+        <v>15866</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -48078,10 +48078,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15316</v>
+        <v>15866</v>
       </c>
       <c r="C20" t="s">
-        <v>15345</v>
+        <v>15866</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -48098,10 +48098,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15317</v>
+        <v>15866</v>
       </c>
       <c r="C21" t="s">
-        <v>15346</v>
+        <v>15866</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -48118,10 +48118,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15318</v>
+        <v>15866</v>
       </c>
       <c r="C22" t="s">
-        <v>15347</v>
+        <v>15866</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -48138,10 +48138,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15319</v>
+        <v>15866</v>
       </c>
       <c r="C23" t="s">
-        <v>15348</v>
+        <v>15866</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -48158,10 +48158,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15320</v>
+        <v>15866</v>
       </c>
       <c r="C24" t="s">
-        <v>15349</v>
+        <v>15866</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -48178,10 +48178,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15321</v>
+        <v>15866</v>
       </c>
       <c r="C25" t="s">
-        <v>15350</v>
+        <v>15866</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -48198,10 +48198,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15322</v>
+        <v>15866</v>
       </c>
       <c r="C26" t="s">
-        <v>15351</v>
+        <v>15866</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -48218,10 +48218,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15323</v>
+        <v>15866</v>
       </c>
       <c r="C27" t="s">
-        <v>15352</v>
+        <v>15866</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -48238,10 +48238,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15324</v>
+        <v>15866</v>
       </c>
       <c r="C28" t="s">
-        <v>15353</v>
+        <v>15866</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -48258,10 +48258,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15325</v>
+        <v>15866</v>
       </c>
       <c r="C29" t="s">
-        <v>15354</v>
+        <v>15866</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -48286,28 +48286,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15360</v>
+        <v>15808</v>
       </c>
       <c r="B1" t="s">
-        <v>15361</v>
+        <v>15809</v>
       </c>
       <c r="C1" t="s">
-        <v>15390</v>
+        <v>15838</v>
       </c>
       <c r="D1" t="s">
-        <v>15419</v>
+        <v>15867</v>
       </c>
       <c r="E1" t="s">
-        <v>15420</v>
+        <v>15868</v>
       </c>
       <c r="F1" t="s">
-        <v>15421</v>
+        <v>15869</v>
       </c>
       <c r="G1" t="s">
-        <v>15422</v>
+        <v>15870</v>
       </c>
       <c r="H1" t="s">
-        <v>15423</v>
+        <v>15871</v>
       </c>
     </row>
     <row r="2">
@@ -48315,10 +48315,10 @@
         <v>2013</v>
       </c>
       <c r="B2" t="s">
-        <v>15362</v>
+        <v>15810</v>
       </c>
       <c r="C2" t="s">
-        <v>15391</v>
+        <v>15839</v>
       </c>
       <c r="D2">
         <v>10193833</v>
@@ -48339,10 +48339,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15363</v>
+        <v>15866</v>
       </c>
       <c r="C3" t="s">
-        <v>15392</v>
+        <v>15866</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -48359,10 +48359,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15364</v>
+        <v>15866</v>
       </c>
       <c r="C4" t="s">
-        <v>15393</v>
+        <v>15866</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -48379,10 +48379,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15365</v>
+        <v>15866</v>
       </c>
       <c r="C5" t="s">
-        <v>15394</v>
+        <v>15866</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -48399,10 +48399,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15366</v>
+        <v>15866</v>
       </c>
       <c r="C6" t="s">
-        <v>15395</v>
+        <v>15866</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -48419,10 +48419,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15367</v>
+        <v>15866</v>
       </c>
       <c r="C7" t="s">
-        <v>15396</v>
+        <v>15866</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -48439,10 +48439,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15368</v>
+        <v>15866</v>
       </c>
       <c r="C8" t="s">
-        <v>15397</v>
+        <v>15866</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -48459,10 +48459,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15369</v>
+        <v>15866</v>
       </c>
       <c r="C9" t="s">
-        <v>15398</v>
+        <v>15866</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -48479,10 +48479,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15370</v>
+        <v>15866</v>
       </c>
       <c r="C10" t="s">
-        <v>15399</v>
+        <v>15866</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -48499,10 +48499,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15371</v>
+        <v>15866</v>
       </c>
       <c r="C11" t="s">
-        <v>15400</v>
+        <v>15866</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -48519,10 +48519,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15372</v>
+        <v>15866</v>
       </c>
       <c r="C12" t="s">
-        <v>15401</v>
+        <v>15866</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -48539,10 +48539,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15373</v>
+        <v>15866</v>
       </c>
       <c r="C13" t="s">
-        <v>15402</v>
+        <v>15866</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -48559,10 +48559,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15374</v>
+        <v>15866</v>
       </c>
       <c r="C14" t="s">
-        <v>15403</v>
+        <v>15866</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -48579,10 +48579,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15375</v>
+        <v>15866</v>
       </c>
       <c r="C15" t="s">
-        <v>15404</v>
+        <v>15866</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -48599,10 +48599,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15376</v>
+        <v>15866</v>
       </c>
       <c r="C16" t="s">
-        <v>15405</v>
+        <v>15866</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -48619,10 +48619,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15377</v>
+        <v>15866</v>
       </c>
       <c r="C17" t="s">
-        <v>15406</v>
+        <v>15866</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -48639,10 +48639,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15378</v>
+        <v>15866</v>
       </c>
       <c r="C18" t="s">
-        <v>15407</v>
+        <v>15866</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -48659,10 +48659,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15379</v>
+        <v>15866</v>
       </c>
       <c r="C19" t="s">
-        <v>15408</v>
+        <v>15866</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -48679,10 +48679,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15380</v>
+        <v>15866</v>
       </c>
       <c r="C20" t="s">
-        <v>15409</v>
+        <v>15866</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -48699,10 +48699,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15381</v>
+        <v>15866</v>
       </c>
       <c r="C21" t="s">
-        <v>15410</v>
+        <v>15866</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -48719,10 +48719,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15382</v>
+        <v>15866</v>
       </c>
       <c r="C22" t="s">
-        <v>15411</v>
+        <v>15866</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -48739,10 +48739,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15383</v>
+        <v>15866</v>
       </c>
       <c r="C23" t="s">
-        <v>15412</v>
+        <v>15866</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -48759,10 +48759,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15384</v>
+        <v>15866</v>
       </c>
       <c r="C24" t="s">
-        <v>15413</v>
+        <v>15866</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -48779,10 +48779,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15385</v>
+        <v>15866</v>
       </c>
       <c r="C25" t="s">
-        <v>15414</v>
+        <v>15866</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -48799,10 +48799,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15386</v>
+        <v>15866</v>
       </c>
       <c r="C26" t="s">
-        <v>15415</v>
+        <v>15866</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -48819,10 +48819,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15387</v>
+        <v>15866</v>
       </c>
       <c r="C27" t="s">
-        <v>15416</v>
+        <v>15866</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -48839,10 +48839,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15388</v>
+        <v>15866</v>
       </c>
       <c r="C28" t="s">
-        <v>15417</v>
+        <v>15866</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -48859,10 +48859,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15389</v>
+        <v>15866</v>
       </c>
       <c r="C29" t="s">
-        <v>15418</v>
+        <v>15866</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -48887,28 +48887,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15424</v>
+        <v>15808</v>
       </c>
       <c r="B1" t="s">
-        <v>15425</v>
+        <v>15809</v>
       </c>
       <c r="C1" t="s">
-        <v>15454</v>
+        <v>15838</v>
       </c>
       <c r="D1" t="s">
-        <v>15483</v>
+        <v>15867</v>
       </c>
       <c r="E1" t="s">
-        <v>15484</v>
+        <v>15868</v>
       </c>
       <c r="F1" t="s">
-        <v>15485</v>
+        <v>15869</v>
       </c>
       <c r="G1" t="s">
-        <v>15486</v>
+        <v>15870</v>
       </c>
       <c r="H1" t="s">
-        <v>15487</v>
+        <v>15871</v>
       </c>
     </row>
     <row r="2">
@@ -48916,10 +48916,10 @@
         <v>2014</v>
       </c>
       <c r="B2" t="s">
-        <v>15426</v>
+        <v>15810</v>
       </c>
       <c r="C2" t="s">
-        <v>15455</v>
+        <v>15839</v>
       </c>
       <c r="D2">
         <v>10315528</v>
@@ -48940,10 +48940,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15427</v>
+        <v>15866</v>
       </c>
       <c r="C3" t="s">
-        <v>15456</v>
+        <v>15866</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -48960,10 +48960,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15428</v>
+        <v>15866</v>
       </c>
       <c r="C4" t="s">
-        <v>15457</v>
+        <v>15866</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -48980,10 +48980,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15429</v>
+        <v>15866</v>
       </c>
       <c r="C5" t="s">
-        <v>15458</v>
+        <v>15866</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -49000,10 +49000,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15430</v>
+        <v>15866</v>
       </c>
       <c r="C6" t="s">
-        <v>15459</v>
+        <v>15866</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -49020,10 +49020,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15431</v>
+        <v>15866</v>
       </c>
       <c r="C7" t="s">
-        <v>15460</v>
+        <v>15866</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -49040,10 +49040,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15432</v>
+        <v>15866</v>
       </c>
       <c r="C8" t="s">
-        <v>15461</v>
+        <v>15866</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -49060,10 +49060,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15433</v>
+        <v>15866</v>
       </c>
       <c r="C9" t="s">
-        <v>15462</v>
+        <v>15866</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -49080,10 +49080,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15434</v>
+        <v>15866</v>
       </c>
       <c r="C10" t="s">
-        <v>15463</v>
+        <v>15866</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -49100,10 +49100,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15435</v>
+        <v>15866</v>
       </c>
       <c r="C11" t="s">
-        <v>15464</v>
+        <v>15866</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -49120,10 +49120,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15436</v>
+        <v>15866</v>
       </c>
       <c r="C12" t="s">
-        <v>15465</v>
+        <v>15866</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -49140,10 +49140,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15437</v>
+        <v>15866</v>
       </c>
       <c r="C13" t="s">
-        <v>15466</v>
+        <v>15866</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -49160,10 +49160,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15438</v>
+        <v>15866</v>
       </c>
       <c r="C14" t="s">
-        <v>15467</v>
+        <v>15866</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -49180,10 +49180,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15439</v>
+        <v>15866</v>
       </c>
       <c r="C15" t="s">
-        <v>15468</v>
+        <v>15866</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -49200,10 +49200,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15440</v>
+        <v>15866</v>
       </c>
       <c r="C16" t="s">
-        <v>15469</v>
+        <v>15866</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -49220,10 +49220,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15441</v>
+        <v>15866</v>
       </c>
       <c r="C17" t="s">
-        <v>15470</v>
+        <v>15866</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -49240,10 +49240,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15442</v>
+        <v>15866</v>
       </c>
       <c r="C18" t="s">
-        <v>15471</v>
+        <v>15866</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -49260,10 +49260,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15443</v>
+        <v>15866</v>
       </c>
       <c r="C19" t="s">
-        <v>15472</v>
+        <v>15866</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -49280,10 +49280,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15444</v>
+        <v>15866</v>
       </c>
       <c r="C20" t="s">
-        <v>15473</v>
+        <v>15866</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -49300,10 +49300,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15445</v>
+        <v>15866</v>
       </c>
       <c r="C21" t="s">
-        <v>15474</v>
+        <v>15866</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -49320,10 +49320,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15446</v>
+        <v>15866</v>
       </c>
       <c r="C22" t="s">
-        <v>15475</v>
+        <v>15866</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -49340,10 +49340,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15447</v>
+        <v>15866</v>
       </c>
       <c r="C23" t="s">
-        <v>15476</v>
+        <v>15866</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -49360,10 +49360,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15448</v>
+        <v>15866</v>
       </c>
       <c r="C24" t="s">
-        <v>15477</v>
+        <v>15866</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -49380,10 +49380,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15449</v>
+        <v>15866</v>
       </c>
       <c r="C25" t="s">
-        <v>15478</v>
+        <v>15866</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -49400,10 +49400,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15450</v>
+        <v>15866</v>
       </c>
       <c r="C26" t="s">
-        <v>15479</v>
+        <v>15866</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -49420,10 +49420,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15451</v>
+        <v>15866</v>
       </c>
       <c r="C27" t="s">
-        <v>15480</v>
+        <v>15866</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -49440,10 +49440,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15452</v>
+        <v>15866</v>
       </c>
       <c r="C28" t="s">
-        <v>15481</v>
+        <v>15866</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -49460,10 +49460,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15453</v>
+        <v>15866</v>
       </c>
       <c r="C29" t="s">
-        <v>15482</v>
+        <v>15866</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -49488,28 +49488,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15488</v>
+        <v>15808</v>
       </c>
       <c r="B1" t="s">
-        <v>15489</v>
+        <v>15809</v>
       </c>
       <c r="C1" t="s">
-        <v>15518</v>
+        <v>15838</v>
       </c>
       <c r="D1" t="s">
-        <v>15547</v>
+        <v>15867</v>
       </c>
       <c r="E1" t="s">
-        <v>15548</v>
+        <v>15868</v>
       </c>
       <c r="F1" t="s">
-        <v>15549</v>
+        <v>15869</v>
       </c>
       <c r="G1" t="s">
-        <v>15550</v>
+        <v>15870</v>
       </c>
       <c r="H1" t="s">
-        <v>15551</v>
+        <v>15871</v>
       </c>
     </row>
     <row r="2">
@@ -49517,10 +49517,10 @@
         <v>2015</v>
       </c>
       <c r="B2" t="s">
-        <v>15490</v>
+        <v>15810</v>
       </c>
       <c r="C2" t="s">
-        <v>15519</v>
+        <v>15839</v>
       </c>
       <c r="D2">
         <v>10434829</v>
@@ -49541,10 +49541,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15491</v>
+        <v>15866</v>
       </c>
       <c r="C3" t="s">
-        <v>15520</v>
+        <v>15866</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -49561,10 +49561,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15492</v>
+        <v>15866</v>
       </c>
       <c r="C4" t="s">
-        <v>15521</v>
+        <v>15866</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -49581,10 +49581,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15493</v>
+        <v>15866</v>
       </c>
       <c r="C5" t="s">
-        <v>15522</v>
+        <v>15866</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -49601,10 +49601,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15494</v>
+        <v>15866</v>
       </c>
       <c r="C6" t="s">
-        <v>15523</v>
+        <v>15866</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -49621,10 +49621,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15495</v>
+        <v>15866</v>
       </c>
       <c r="C7" t="s">
-        <v>15524</v>
+        <v>15866</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -49641,10 +49641,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15496</v>
+        <v>15866</v>
       </c>
       <c r="C8" t="s">
-        <v>15525</v>
+        <v>15866</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -49661,10 +49661,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15497</v>
+        <v>15866</v>
       </c>
       <c r="C9" t="s">
-        <v>15526</v>
+        <v>15866</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -49681,10 +49681,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15498</v>
+        <v>15866</v>
       </c>
       <c r="C10" t="s">
-        <v>15527</v>
+        <v>15866</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -49701,10 +49701,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15499</v>
+        <v>15866</v>
       </c>
       <c r="C11" t="s">
-        <v>15528</v>
+        <v>15866</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -49721,10 +49721,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15500</v>
+        <v>15866</v>
       </c>
       <c r="C12" t="s">
-        <v>15529</v>
+        <v>15866</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -49741,10 +49741,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15501</v>
+        <v>15866</v>
       </c>
       <c r="C13" t="s">
-        <v>15530</v>
+        <v>15866</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -49761,10 +49761,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15502</v>
+        <v>15866</v>
       </c>
       <c r="C14" t="s">
-        <v>15531</v>
+        <v>15866</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -49781,10 +49781,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15503</v>
+        <v>15866</v>
       </c>
       <c r="C15" t="s">
-        <v>15532</v>
+        <v>15866</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -49801,10 +49801,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15504</v>
+        <v>15866</v>
       </c>
       <c r="C16" t="s">
-        <v>15533</v>
+        <v>15866</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -49821,10 +49821,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15505</v>
+        <v>15866</v>
       </c>
       <c r="C17" t="s">
-        <v>15534</v>
+        <v>15866</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -49841,10 +49841,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15506</v>
+        <v>15866</v>
       </c>
       <c r="C18" t="s">
-        <v>15535</v>
+        <v>15866</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -49861,10 +49861,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15507</v>
+        <v>15866</v>
       </c>
       <c r="C19" t="s">
-        <v>15536</v>
+        <v>15866</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -49881,10 +49881,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15508</v>
+        <v>15866</v>
       </c>
       <c r="C20" t="s">
-        <v>15537</v>
+        <v>15866</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -49901,10 +49901,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15509</v>
+        <v>15866</v>
       </c>
       <c r="C21" t="s">
-        <v>15538</v>
+        <v>15866</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -49921,10 +49921,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15510</v>
+        <v>15866</v>
       </c>
       <c r="C22" t="s">
-        <v>15539</v>
+        <v>15866</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -49941,10 +49941,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15511</v>
+        <v>15866</v>
       </c>
       <c r="C23" t="s">
-        <v>15540</v>
+        <v>15866</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -49961,10 +49961,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15512</v>
+        <v>15866</v>
       </c>
       <c r="C24" t="s">
-        <v>15541</v>
+        <v>15866</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -49981,10 +49981,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15513</v>
+        <v>15866</v>
       </c>
       <c r="C25" t="s">
-        <v>15542</v>
+        <v>15866</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -50001,10 +50001,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15514</v>
+        <v>15866</v>
       </c>
       <c r="C26" t="s">
-        <v>15543</v>
+        <v>15866</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -50021,10 +50021,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15515</v>
+        <v>15866</v>
       </c>
       <c r="C27" t="s">
-        <v>15544</v>
+        <v>15866</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -50041,10 +50041,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15516</v>
+        <v>15866</v>
       </c>
       <c r="C28" t="s">
-        <v>15545</v>
+        <v>15866</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -50061,10 +50061,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15517</v>
+        <v>15866</v>
       </c>
       <c r="C29" t="s">
-        <v>15546</v>
+        <v>15866</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -50089,28 +50089,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15552</v>
+        <v>15808</v>
       </c>
       <c r="B1" t="s">
-        <v>15553</v>
+        <v>15809</v>
       </c>
       <c r="C1" t="s">
-        <v>15582</v>
+        <v>15838</v>
       </c>
       <c r="D1" t="s">
-        <v>15611</v>
+        <v>15867</v>
       </c>
       <c r="E1" t="s">
-        <v>15612</v>
+        <v>15868</v>
       </c>
       <c r="F1" t="s">
-        <v>15613</v>
+        <v>15869</v>
       </c>
       <c r="G1" t="s">
-        <v>15614</v>
+        <v>15870</v>
       </c>
       <c r="H1" t="s">
-        <v>15615</v>
+        <v>15871</v>
       </c>
     </row>
     <row r="2">
@@ -50118,10 +50118,10 @@
         <v>2016</v>
       </c>
       <c r="B2" t="s">
-        <v>15554</v>
+        <v>15810</v>
       </c>
       <c r="C2" t="s">
-        <v>15583</v>
+        <v>15839</v>
       </c>
       <c r="D2">
         <v>10551430</v>
@@ -50142,10 +50142,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15555</v>
+        <v>15866</v>
       </c>
       <c r="C3" t="s">
-        <v>15584</v>
+        <v>15866</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -50162,10 +50162,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15556</v>
+        <v>15866</v>
       </c>
       <c r="C4" t="s">
-        <v>15585</v>
+        <v>15866</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -50182,10 +50182,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15557</v>
+        <v>15866</v>
       </c>
       <c r="C5" t="s">
-        <v>15586</v>
+        <v>15866</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -50202,10 +50202,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15558</v>
+        <v>15866</v>
       </c>
       <c r="C6" t="s">
-        <v>15587</v>
+        <v>15866</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -50222,10 +50222,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15559</v>
+        <v>15866</v>
       </c>
       <c r="C7" t="s">
-        <v>15588</v>
+        <v>15866</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -50242,10 +50242,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15560</v>
+        <v>15866</v>
       </c>
       <c r="C8" t="s">
-        <v>15589</v>
+        <v>15866</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -50262,10 +50262,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15561</v>
+        <v>15866</v>
       </c>
       <c r="C9" t="s">
-        <v>15590</v>
+        <v>15866</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -50282,10 +50282,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15562</v>
+        <v>15866</v>
       </c>
       <c r="C10" t="s">
-        <v>15591</v>
+        <v>15866</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -50302,10 +50302,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15563</v>
+        <v>15866</v>
       </c>
       <c r="C11" t="s">
-        <v>15592</v>
+        <v>15866</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -50322,10 +50322,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15564</v>
+        <v>15866</v>
       </c>
       <c r="C12" t="s">
-        <v>15593</v>
+        <v>15866</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -50342,10 +50342,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15565</v>
+        <v>15866</v>
       </c>
       <c r="C13" t="s">
-        <v>15594</v>
+        <v>15866</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -50362,10 +50362,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15566</v>
+        <v>15866</v>
       </c>
       <c r="C14" t="s">
-        <v>15595</v>
+        <v>15866</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -50382,10 +50382,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15567</v>
+        <v>15866</v>
       </c>
       <c r="C15" t="s">
-        <v>15596</v>
+        <v>15866</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -50402,10 +50402,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15568</v>
+        <v>15866</v>
       </c>
       <c r="C16" t="s">
-        <v>15597</v>
+        <v>15866</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -50422,10 +50422,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15569</v>
+        <v>15866</v>
       </c>
       <c r="C17" t="s">
-        <v>15598</v>
+        <v>15866</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -50442,10 +50442,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15570</v>
+        <v>15866</v>
       </c>
       <c r="C18" t="s">
-        <v>15599</v>
+        <v>15866</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -50462,10 +50462,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15571</v>
+        <v>15866</v>
       </c>
       <c r="C19" t="s">
-        <v>15600</v>
+        <v>15866</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -50482,10 +50482,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15572</v>
+        <v>15866</v>
       </c>
       <c r="C20" t="s">
-        <v>15601</v>
+        <v>15866</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -50502,10 +50502,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15573</v>
+        <v>15866</v>
       </c>
       <c r="C21" t="s">
-        <v>15602</v>
+        <v>15866</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -50522,10 +50522,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15574</v>
+        <v>15866</v>
       </c>
       <c r="C22" t="s">
-        <v>15603</v>
+        <v>15866</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -50542,10 +50542,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15575</v>
+        <v>15866</v>
       </c>
       <c r="C23" t="s">
-        <v>15604</v>
+        <v>15866</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -50562,10 +50562,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15576</v>
+        <v>15866</v>
       </c>
       <c r="C24" t="s">
-        <v>15605</v>
+        <v>15866</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -50582,10 +50582,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15577</v>
+        <v>15866</v>
       </c>
       <c r="C25" t="s">
-        <v>15606</v>
+        <v>15866</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -50602,10 +50602,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15578</v>
+        <v>15866</v>
       </c>
       <c r="C26" t="s">
-        <v>15607</v>
+        <v>15866</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -50622,10 +50622,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15579</v>
+        <v>15866</v>
       </c>
       <c r="C27" t="s">
-        <v>15608</v>
+        <v>15866</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -50642,10 +50642,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15580</v>
+        <v>15866</v>
       </c>
       <c r="C28" t="s">
-        <v>15609</v>
+        <v>15866</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -50662,10 +50662,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15581</v>
+        <v>15866</v>
       </c>
       <c r="C29" t="s">
-        <v>15610</v>
+        <v>15866</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -50690,28 +50690,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15616</v>
+        <v>15808</v>
       </c>
       <c r="B1" t="s">
-        <v>15617</v>
+        <v>15809</v>
       </c>
       <c r="C1" t="s">
-        <v>15646</v>
+        <v>15838</v>
       </c>
       <c r="D1" t="s">
-        <v>15675</v>
+        <v>15867</v>
       </c>
       <c r="E1" t="s">
-        <v>15676</v>
+        <v>15868</v>
       </c>
       <c r="F1" t="s">
-        <v>15677</v>
+        <v>15869</v>
       </c>
       <c r="G1" t="s">
-        <v>15678</v>
+        <v>15870</v>
       </c>
       <c r="H1" t="s">
-        <v>15679</v>
+        <v>15871</v>
       </c>
     </row>
     <row r="2">
@@ -50719,10 +50719,10 @@
         <v>2017</v>
       </c>
       <c r="B2" t="s">
-        <v>15618</v>
+        <v>15810</v>
       </c>
       <c r="C2" t="s">
-        <v>15647</v>
+        <v>15839</v>
       </c>
       <c r="D2">
         <v>10666843</v>
@@ -50743,10 +50743,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15619</v>
+        <v>15866</v>
       </c>
       <c r="C3" t="s">
-        <v>15648</v>
+        <v>15866</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -50763,10 +50763,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15620</v>
+        <v>15866</v>
       </c>
       <c r="C4" t="s">
-        <v>15649</v>
+        <v>15866</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -50783,10 +50783,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15621</v>
+        <v>15866</v>
       </c>
       <c r="C5" t="s">
-        <v>15650</v>
+        <v>15866</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -50803,10 +50803,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15622</v>
+        <v>15866</v>
       </c>
       <c r="C6" t="s">
-        <v>15651</v>
+        <v>15866</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -50823,10 +50823,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15623</v>
+        <v>15866</v>
       </c>
       <c r="C7" t="s">
-        <v>15652</v>
+        <v>15866</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -50843,10 +50843,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15624</v>
+        <v>15866</v>
       </c>
       <c r="C8" t="s">
-        <v>15653</v>
+        <v>15866</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -50863,10 +50863,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15625</v>
+        <v>15866</v>
       </c>
       <c r="C9" t="s">
-        <v>15654</v>
+        <v>15866</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -50883,10 +50883,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15626</v>
+        <v>15866</v>
       </c>
       <c r="C10" t="s">
-        <v>15655</v>
+        <v>15866</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -50903,10 +50903,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15627</v>
+        <v>15866</v>
       </c>
       <c r="C11" t="s">
-        <v>15656</v>
+        <v>15866</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -50923,10 +50923,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15628</v>
+        <v>15866</v>
       </c>
       <c r="C12" t="s">
-        <v>15657</v>
+        <v>15866</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -50943,10 +50943,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15629</v>
+        <v>15866</v>
       </c>
       <c r="C13" t="s">
-        <v>15658</v>
+        <v>15866</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -50963,10 +50963,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15630</v>
+        <v>15866</v>
       </c>
       <c r="C14" t="s">
-        <v>15659</v>
+        <v>15866</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -50983,10 +50983,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15631</v>
+        <v>15866</v>
       </c>
       <c r="C15" t="s">
-        <v>15660</v>
+        <v>15866</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -51003,10 +51003,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15632</v>
+        <v>15866</v>
       </c>
       <c r="C16" t="s">
-        <v>15661</v>
+        <v>15866</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -51023,10 +51023,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15633</v>
+        <v>15866</v>
       </c>
       <c r="C17" t="s">
-        <v>15662</v>
+        <v>15866</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -51043,10 +51043,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15634</v>
+        <v>15866</v>
       </c>
       <c r="C18" t="s">
-        <v>15663</v>
+        <v>15866</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -51063,10 +51063,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15635</v>
+        <v>15866</v>
       </c>
       <c r="C19" t="s">
-        <v>15664</v>
+        <v>15866</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -51083,10 +51083,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15636</v>
+        <v>15866</v>
       </c>
       <c r="C20" t="s">
-        <v>15665</v>
+        <v>15866</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -51103,10 +51103,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15637</v>
+        <v>15866</v>
       </c>
       <c r="C21" t="s">
-        <v>15666</v>
+        <v>15866</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -51123,10 +51123,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15638</v>
+        <v>15866</v>
       </c>
       <c r="C22" t="s">
-        <v>15667</v>
+        <v>15866</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -51143,10 +51143,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15639</v>
+        <v>15866</v>
       </c>
       <c r="C23" t="s">
-        <v>15668</v>
+        <v>15866</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -51163,10 +51163,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15640</v>
+        <v>15866</v>
       </c>
       <c r="C24" t="s">
-        <v>15669</v>
+        <v>15866</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -51183,10 +51183,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15641</v>
+        <v>15866</v>
       </c>
       <c r="C25" t="s">
-        <v>15670</v>
+        <v>15866</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -51203,10 +51203,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15642</v>
+        <v>15866</v>
       </c>
       <c r="C26" t="s">
-        <v>15671</v>
+        <v>15866</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -51223,10 +51223,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15643</v>
+        <v>15866</v>
       </c>
       <c r="C27" t="s">
-        <v>15672</v>
+        <v>15866</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -51243,10 +51243,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15644</v>
+        <v>15866</v>
       </c>
       <c r="C28" t="s">
-        <v>15673</v>
+        <v>15866</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -51263,10 +51263,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15645</v>
+        <v>15866</v>
       </c>
       <c r="C29" t="s">
-        <v>15674</v>
+        <v>15866</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -51291,28 +51291,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15680</v>
+        <v>15808</v>
       </c>
       <c r="B1" t="s">
-        <v>15681</v>
+        <v>15809</v>
       </c>
       <c r="C1" t="s">
-        <v>15710</v>
+        <v>15838</v>
       </c>
       <c r="D1" t="s">
-        <v>15739</v>
+        <v>15867</v>
       </c>
       <c r="E1" t="s">
-        <v>15740</v>
+        <v>15868</v>
       </c>
       <c r="F1" t="s">
-        <v>15741</v>
+        <v>15869</v>
       </c>
       <c r="G1" t="s">
-        <v>15742</v>
+        <v>15870</v>
       </c>
       <c r="H1" t="s">
-        <v>15743</v>
+        <v>15871</v>
       </c>
     </row>
     <row r="2">
@@ -51320,10 +51320,10 @@
         <v>2018</v>
       </c>
       <c r="B2" t="s">
-        <v>15682</v>
+        <v>15810</v>
       </c>
       <c r="C2" t="s">
-        <v>15711</v>
+        <v>15839</v>
       </c>
       <c r="D2">
         <v>10782053</v>
@@ -51344,10 +51344,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15683</v>
+        <v>15866</v>
       </c>
       <c r="C3" t="s">
-        <v>15712</v>
+        <v>15866</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -51364,10 +51364,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15684</v>
+        <v>15866</v>
       </c>
       <c r="C4" t="s">
-        <v>15713</v>
+        <v>15866</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -51384,10 +51384,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15685</v>
+        <v>15866</v>
       </c>
       <c r="C5" t="s">
-        <v>15714</v>
+        <v>15866</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -51404,10 +51404,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15686</v>
+        <v>15866</v>
       </c>
       <c r="C6" t="s">
-        <v>15715</v>
+        <v>15866</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -51424,10 +51424,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15687</v>
+        <v>15866</v>
       </c>
       <c r="C7" t="s">
-        <v>15716</v>
+        <v>15866</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -51444,10 +51444,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15688</v>
+        <v>15866</v>
       </c>
       <c r="C8" t="s">
-        <v>15717</v>
+        <v>15866</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -51464,10 +51464,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15689</v>
+        <v>15866</v>
       </c>
       <c r="C9" t="s">
-        <v>15718</v>
+        <v>15866</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -51484,10 +51484,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15690</v>
+        <v>15866</v>
       </c>
       <c r="C10" t="s">
-        <v>15719</v>
+        <v>15866</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -51504,10 +51504,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15691</v>
+        <v>15866</v>
       </c>
       <c r="C11" t="s">
-        <v>15720</v>
+        <v>15866</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -51524,10 +51524,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15692</v>
+        <v>15866</v>
       </c>
       <c r="C12" t="s">
-        <v>15721</v>
+        <v>15866</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -51544,10 +51544,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15693</v>
+        <v>15866</v>
       </c>
       <c r="C13" t="s">
-        <v>15722</v>
+        <v>15866</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -51564,10 +51564,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15694</v>
+        <v>15866</v>
       </c>
       <c r="C14" t="s">
-        <v>15723</v>
+        <v>15866</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -51584,10 +51584,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15695</v>
+        <v>15866</v>
       </c>
       <c r="C15" t="s">
-        <v>15724</v>
+        <v>15866</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -51604,10 +51604,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15696</v>
+        <v>15866</v>
       </c>
       <c r="C16" t="s">
-        <v>15725</v>
+        <v>15866</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -51624,10 +51624,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15697</v>
+        <v>15866</v>
       </c>
       <c r="C17" t="s">
-        <v>15726</v>
+        <v>15866</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -51644,10 +51644,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15698</v>
+        <v>15866</v>
       </c>
       <c r="C18" t="s">
-        <v>15727</v>
+        <v>15866</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -51664,10 +51664,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15699</v>
+        <v>15866</v>
       </c>
       <c r="C19" t="s">
-        <v>15728</v>
+        <v>15866</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -51684,10 +51684,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15700</v>
+        <v>15866</v>
       </c>
       <c r="C20" t="s">
-        <v>15729</v>
+        <v>15866</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -51704,10 +51704,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15701</v>
+        <v>15866</v>
       </c>
       <c r="C21" t="s">
-        <v>15730</v>
+        <v>15866</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -51724,10 +51724,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15702</v>
+        <v>15866</v>
       </c>
       <c r="C22" t="s">
-        <v>15731</v>
+        <v>15866</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -51744,10 +51744,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15703</v>
+        <v>15866</v>
       </c>
       <c r="C23" t="s">
-        <v>15732</v>
+        <v>15866</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -51764,10 +51764,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15704</v>
+        <v>15866</v>
       </c>
       <c r="C24" t="s">
-        <v>15733</v>
+        <v>15866</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -51784,10 +51784,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15705</v>
+        <v>15866</v>
       </c>
       <c r="C25" t="s">
-        <v>15734</v>
+        <v>15866</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -51804,10 +51804,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15706</v>
+        <v>15866</v>
       </c>
       <c r="C26" t="s">
-        <v>15735</v>
+        <v>15866</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -51824,10 +51824,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15707</v>
+        <v>15866</v>
       </c>
       <c r="C27" t="s">
-        <v>15736</v>
+        <v>15866</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -51844,10 +51844,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15708</v>
+        <v>15866</v>
       </c>
       <c r="C28" t="s">
-        <v>15737</v>
+        <v>15866</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -51864,10 +51864,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15709</v>
+        <v>15866</v>
       </c>
       <c r="C29" t="s">
-        <v>15738</v>
+        <v>15866</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -51892,28 +51892,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>15744</v>
+        <v>15808</v>
       </c>
       <c r="B1" t="s">
-        <v>15745</v>
+        <v>15809</v>
       </c>
       <c r="C1" t="s">
-        <v>15774</v>
+        <v>15838</v>
       </c>
       <c r="D1" t="s">
-        <v>15803</v>
+        <v>15867</v>
       </c>
       <c r="E1" t="s">
-        <v>15804</v>
+        <v>15868</v>
       </c>
       <c r="F1" t="s">
-        <v>15805</v>
+        <v>15869</v>
       </c>
       <c r="G1" t="s">
-        <v>15806</v>
+        <v>15870</v>
       </c>
       <c r="H1" t="s">
-        <v>15807</v>
+        <v>15871</v>
       </c>
     </row>
     <row r="2">
@@ -51921,10 +51921,10 @@
         <v>2019</v>
       </c>
       <c r="B2" t="s">
-        <v>15746</v>
+        <v>15810</v>
       </c>
       <c r="C2" t="s">
-        <v>15775</v>
+        <v>15839</v>
       </c>
       <c r="D2">
         <v>10894043</v>
@@ -51945,10 +51945,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15747</v>
+        <v>15866</v>
       </c>
       <c r="C3" t="s">
-        <v>15776</v>
+        <v>15866</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -51965,10 +51965,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15748</v>
+        <v>15866</v>
       </c>
       <c r="C4" t="s">
-        <v>15777</v>
+        <v>15866</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -51985,10 +51985,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15749</v>
+        <v>15866</v>
       </c>
       <c r="C5" t="s">
-        <v>15778</v>
+        <v>15866</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -52005,10 +52005,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15750</v>
+        <v>15866</v>
       </c>
       <c r="C6" t="s">
-        <v>15779</v>
+        <v>15866</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -52025,10 +52025,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15751</v>
+        <v>15866</v>
       </c>
       <c r="C7" t="s">
-        <v>15780</v>
+        <v>15866</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -52045,10 +52045,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15752</v>
+        <v>15866</v>
       </c>
       <c r="C8" t="s">
-        <v>15781</v>
+        <v>15866</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -52065,10 +52065,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15753</v>
+        <v>15866</v>
       </c>
       <c r="C9" t="s">
-        <v>15782</v>
+        <v>15866</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -52085,10 +52085,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15754</v>
+        <v>15866</v>
       </c>
       <c r="C10" t="s">
-        <v>15783</v>
+        <v>15866</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -52105,10 +52105,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15755</v>
+        <v>15866</v>
       </c>
       <c r="C11" t="s">
-        <v>15784</v>
+        <v>15866</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -52125,10 +52125,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15756</v>
+        <v>15866</v>
       </c>
       <c r="C12" t="s">
-        <v>15785</v>
+        <v>15866</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -52145,10 +52145,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15757</v>
+        <v>15866</v>
       </c>
       <c r="C13" t="s">
-        <v>15786</v>
+        <v>15866</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -52165,10 +52165,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15758</v>
+        <v>15866</v>
       </c>
       <c r="C14" t="s">
-        <v>15787</v>
+        <v>15866</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -52185,10 +52185,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15759</v>
+        <v>15866</v>
       </c>
       <c r="C15" t="s">
-        <v>15788</v>
+        <v>15866</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -52205,10 +52205,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15760</v>
+        <v>15866</v>
       </c>
       <c r="C16" t="s">
-        <v>15789</v>
+        <v>15866</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -52225,10 +52225,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15761</v>
+        <v>15866</v>
       </c>
       <c r="C17" t="s">
-        <v>15790</v>
+        <v>15866</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -52245,10 +52245,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15762</v>
+        <v>15866</v>
       </c>
       <c r="C18" t="s">
-        <v>15791</v>
+        <v>15866</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -52265,10 +52265,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15763</v>
+        <v>15866</v>
       </c>
       <c r="C19" t="s">
-        <v>15792</v>
+        <v>15866</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -52285,10 +52285,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15764</v>
+        <v>15866</v>
       </c>
       <c r="C20" t="s">
-        <v>15793</v>
+        <v>15866</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -52305,10 +52305,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15765</v>
+        <v>15866</v>
       </c>
       <c r="C21" t="s">
-        <v>15794</v>
+        <v>15866</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -52325,10 +52325,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15766</v>
+        <v>15866</v>
       </c>
       <c r="C22" t="s">
-        <v>15795</v>
+        <v>15866</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -52345,10 +52345,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15767</v>
+        <v>15866</v>
       </c>
       <c r="C23" t="s">
-        <v>15796</v>
+        <v>15866</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -52365,10 +52365,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15768</v>
+        <v>15866</v>
       </c>
       <c r="C24" t="s">
-        <v>15797</v>
+        <v>15866</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -52385,10 +52385,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15769</v>
+        <v>15866</v>
       </c>
       <c r="C25" t="s">
-        <v>15798</v>
+        <v>15866</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -52405,10 +52405,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15770</v>
+        <v>15866</v>
       </c>
       <c r="C26" t="s">
-        <v>15799</v>
+        <v>15866</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -52425,10 +52425,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15771</v>
+        <v>15866</v>
       </c>
       <c r="C27" t="s">
-        <v>15800</v>
+        <v>15866</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -52445,10 +52445,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15772</v>
+        <v>15866</v>
       </c>
       <c r="C28" t="s">
-        <v>15801</v>
+        <v>15866</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -52465,10 +52465,10 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15773</v>
+        <v>15866</v>
       </c>
       <c r="C29" t="s">
-        <v>15802</v>
+        <v>15866</v>
       </c>
       <c r="D29"/>
       <c r="E29"/>
@@ -52546,10 +52546,10 @@
     <row r="3">
       <c r="A3"/>
       <c r="B3" t="s">
-        <v>15811</v>
+        <v>15866</v>
       </c>
       <c r="C3" t="s">
-        <v>15840</v>
+        <v>15866</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -52566,10 +52566,10 @@
     <row r="4">
       <c r="A4"/>
       <c r="B4" t="s">
-        <v>15812</v>
+        <v>15866</v>
       </c>
       <c r="C4" t="s">
-        <v>15841</v>
+        <v>15866</v>
       </c>
       <c r="D4"/>
       <c r="E4"/>
@@ -52586,10 +52586,10 @@
     <row r="5">
       <c r="A5"/>
       <c r="B5" t="s">
-        <v>15813</v>
+        <v>15866</v>
       </c>
       <c r="C5" t="s">
-        <v>15842</v>
+        <v>15866</v>
       </c>
       <c r="D5"/>
       <c r="E5"/>
@@ -52606,10 +52606,10 @@
     <row r="6">
       <c r="A6"/>
       <c r="B6" t="s">
-        <v>15814</v>
+        <v>15866</v>
       </c>
       <c r="C6" t="s">
-        <v>15843</v>
+        <v>15866</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -52626,10 +52626,10 @@
     <row r="7">
       <c r="A7"/>
       <c r="B7" t="s">
-        <v>15815</v>
+        <v>15866</v>
       </c>
       <c r="C7" t="s">
-        <v>15844</v>
+        <v>15866</v>
       </c>
       <c r="D7"/>
       <c r="E7"/>
@@ -52646,10 +52646,10 @@
     <row r="8">
       <c r="A8"/>
       <c r="B8" t="s">
-        <v>15816</v>
+        <v>15866</v>
       </c>
       <c r="C8" t="s">
-        <v>15845</v>
+        <v>15866</v>
       </c>
       <c r="D8"/>
       <c r="E8"/>
@@ -52666,10 +52666,10 @@
     <row r="9">
       <c r="A9"/>
       <c r="B9" t="s">
-        <v>15817</v>
+        <v>15866</v>
       </c>
       <c r="C9" t="s">
-        <v>15846</v>
+        <v>15866</v>
       </c>
       <c r="D9"/>
       <c r="E9"/>
@@ -52686,10 +52686,10 @@
     <row r="10">
       <c r="A10"/>
       <c r="B10" t="s">
-        <v>15818</v>
+        <v>15866</v>
       </c>
       <c r="C10" t="s">
-        <v>15847</v>
+        <v>15866</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
@@ -52706,10 +52706,10 @@
     <row r="11">
       <c r="A11"/>
       <c r="B11" t="s">
-        <v>15819</v>
+        <v>15866</v>
       </c>
       <c r="C11" t="s">
-        <v>15848</v>
+        <v>15866</v>
       </c>
       <c r="D11"/>
       <c r="E11"/>
@@ -52726,10 +52726,10 @@
     <row r="12">
       <c r="A12"/>
       <c r="B12" t="s">
-        <v>15820</v>
+        <v>15866</v>
       </c>
       <c r="C12" t="s">
-        <v>15849</v>
+        <v>15866</v>
       </c>
       <c r="D12"/>
       <c r="E12"/>
@@ -52746,10 +52746,10 @@
     <row r="13">
       <c r="A13"/>
       <c r="B13" t="s">
-        <v>15821</v>
+        <v>15866</v>
       </c>
       <c r="C13" t="s">
-        <v>15850</v>
+        <v>15866</v>
       </c>
       <c r="D13"/>
       <c r="E13"/>
@@ -52766,10 +52766,10 @@
     <row r="14">
       <c r="A14"/>
       <c r="B14" t="s">
-        <v>15822</v>
+        <v>15866</v>
       </c>
       <c r="C14" t="s">
-        <v>15851</v>
+        <v>15866</v>
       </c>
       <c r="D14"/>
       <c r="E14"/>
@@ -52786,10 +52786,10 @@
     <row r="15">
       <c r="A15"/>
       <c r="B15" t="s">
-        <v>15823</v>
+        <v>15866</v>
       </c>
       <c r="C15" t="s">
-        <v>15852</v>
+        <v>15866</v>
       </c>
       <c r="D15"/>
       <c r="E15"/>
@@ -52806,10 +52806,10 @@
     <row r="16">
       <c r="A16"/>
       <c r="B16" t="s">
-        <v>15824</v>
+        <v>15866</v>
       </c>
       <c r="C16" t="s">
-        <v>15853</v>
+        <v>15866</v>
       </c>
       <c r="D16"/>
       <c r="E16"/>
@@ -52826,10 +52826,10 @@
     <row r="17">
       <c r="A17"/>
       <c r="B17" t="s">
-        <v>15825</v>
+        <v>15866</v>
       </c>
       <c r="C17" t="s">
-        <v>15854</v>
+        <v>15866</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
@@ -52846,10 +52846,10 @@
     <row r="18">
       <c r="A18"/>
       <c r="B18" t="s">
-        <v>15826</v>
+        <v>15866</v>
       </c>
       <c r="C18" t="s">
-        <v>15855</v>
+        <v>15866</v>
       </c>
       <c r="D18"/>
       <c r="E18"/>
@@ -52866,10 +52866,10 @@
     <row r="19">
       <c r="A19"/>
       <c r="B19" t="s">
-        <v>15827</v>
+        <v>15866</v>
       </c>
       <c r="C19" t="s">
-        <v>15856</v>
+        <v>15866</v>
       </c>
       <c r="D19"/>
       <c r="E19"/>
@@ -52886,10 +52886,10 @@
     <row r="20">
       <c r="A20"/>
       <c r="B20" t="s">
-        <v>15828</v>
+        <v>15866</v>
       </c>
       <c r="C20" t="s">
-        <v>15857</v>
+        <v>15866</v>
       </c>
       <c r="D20"/>
       <c r="E20"/>
@@ -52906,10 +52906,10 @@
     <row r="21">
       <c r="A21"/>
       <c r="B21" t="s">
-        <v>15829</v>
+        <v>15866</v>
       </c>
       <c r="C21" t="s">
-        <v>15858</v>
+        <v>15866</v>
       </c>
       <c r="D21"/>
       <c r="E21"/>
@@ -52926,10 +52926,10 @@
     <row r="22">
       <c r="A22"/>
       <c r="B22" t="s">
-        <v>15830</v>
+        <v>15866</v>
       </c>
       <c r="C22" t="s">
-        <v>15859</v>
+        <v>15866</v>
       </c>
       <c r="D22"/>
       <c r="E22"/>
@@ -52946,10 +52946,10 @@
     <row r="23">
       <c r="A23"/>
       <c r="B23" t="s">
-        <v>15831</v>
+        <v>15866</v>
       </c>
       <c r="C23" t="s">
-        <v>15860</v>
+        <v>15866</v>
       </c>
       <c r="D23"/>
       <c r="E23"/>
@@ -52966,10 +52966,10 @@
     <row r="24">
       <c r="A24"/>
       <c r="B24" t="s">
-        <v>15832</v>
+        <v>15866</v>
       </c>
       <c r="C24" t="s">
-        <v>15861</v>
+        <v>15866</v>
       </c>
       <c r="D24"/>
       <c r="E24"/>
@@ -52986,10 +52986,10 @@
     <row r="25">
       <c r="A25"/>
       <c r="B25" t="s">
-        <v>15833</v>
+        <v>15866</v>
       </c>
       <c r="C25" t="s">
-        <v>15862</v>
+        <v>15866</v>
       </c>
       <c r="D25"/>
       <c r="E25"/>
@@ -53006,10 +53006,10 @@
     <row r="26">
       <c r="A26"/>
       <c r="B26" t="s">
-        <v>15834</v>
+        <v>15866</v>
       </c>
       <c r="C26" t="s">
-        <v>15863</v>
+        <v>15866</v>
       </c>
       <c r="D26"/>
       <c r="E26"/>
@@ -53026,10 +53026,10 @@
     <row r="27">
       <c r="A27"/>
       <c r="B27" t="s">
-        <v>15835</v>
+        <v>15866</v>
       </c>
       <c r="C27" t="s">
-        <v>15864</v>
+        <v>15866</v>
       </c>
       <c r="D27"/>
       <c r="E27"/>
@@ -53046,10 +53046,10 @@
     <row r="28">
       <c r="A28"/>
       <c r="B28" t="s">
-        <v>15836</v>
+        <v>15866</v>
       </c>
       <c r="C28" t="s">
-        <v>15865</v>
+        <v>15866</v>
       </c>
       <c r="D28"/>
       <c r="E28"/>
@@ -53066,7 +53066,7 @@
     <row r="29">
       <c r="A29"/>
       <c r="B29" t="s">
-        <v>15837</v>
+        <v>15866</v>
       </c>
       <c r="C29" t="s">
         <v>15866</v>

--- a/input_data/admin_data/DOM/_clean/total-pre-DOM.xlsx
+++ b/input_data/admin_data/DOM/_clean/total-pre-DOM.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22784" uniqueCount="15872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23360" uniqueCount="15872">
   <si>
     <t>year</t>
   </si>

--- a/input_data/admin_data/DOM/_clean/total-pre-DOM.xlsx
+++ b/input_data/admin_data/DOM/_clean/total-pre-DOM.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="11">
   <si>
     <t>year</t>
   </si>
